--- a/source_data/SourceData_EDFig2.xlsx
+++ b/source_data/SourceData_EDFig2.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>analysis/meoh_pruning_2026_10_06/candidate_bounds.csv; evaluated/excluded re-derived with the agent rule of run_meoh_pruning.py and checked per group against group_pruning.csv</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/pruning/candidate_bounds.csv; evaluated/excluded re-derived with the agent rule of run_meoh_pruning.py and checked per group against group_pruning.csv</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -514,7 +514,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/meoh_pruning_2026_10_06/summary.json, analysis/nh3_alloy_extension_2026_10_05/nh3_1_2/summary.json (pruning) and analysis/nh3_alloy_extension_2026_10_05/nh3_1_2/alloy_chain_results.csv</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/pruning/summary.json, analysis/nh3_alloy_extension_2026_10_05/nh3_1_2/summary.json (pruning) and analysis/nh3_alloy_extension_2026_10_05/nh3_1_2/alloy_chain_results.csv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G313"/>
+  <dimension ref="A1:G635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_pruning_2026_10_06/candidate_bounds.csv; evaluated/excluded re-derived with the agent rule of run_meoh_pruning.py and checked per group against group_pruning.csv</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/pruning/candidate_bounds.csv; evaluated/excluded re-derived with the agent rule of run_meoh_pruning.py and checked per group against group_pruning.csv</t>
         </is>
       </c>
     </row>
@@ -8983,6 +8983,8700 @@
       </c>
       <c r="G313" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>10.1002/cbh2.70072 | 30 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Figure 1a/text, Cu/ZnGa, 240°C</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>868.659</v>
+      </c>
+      <c r="D314" t="n">
+        <v>876.723</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1413.44</v>
+      </c>
+      <c r="F314" t="b">
+        <v>1</v>
+      </c>
+      <c r="G314" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>10.1002/cbh2.70072 | 30 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Figure 1b/text, Cu/ZnCr, 240°C</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>876.028</v>
+      </c>
+      <c r="D315" t="n">
+        <v>880.353</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1563.02</v>
+      </c>
+      <c r="F315" t="b">
+        <v>1</v>
+      </c>
+      <c r="G315" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>10.1002/cbh2.70072 | 30 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Figure 1c/text, Cu/ZnAl, 240°C</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>881.282</v>
+      </c>
+      <c r="D316" t="n">
+        <v>883.708</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1624.43</v>
+      </c>
+      <c r="F316" t="b">
+        <v>0</v>
+      </c>
+      <c r="G316" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>10.1007/s11426-026-3904-1 | 20 bar | H2/CO2 3 | 6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Figure 1A/B and text, CuZnAl, 230 °C</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>876.144</v>
+      </c>
+      <c r="D317" t="n">
+        <v>878.943</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1049.54</v>
+      </c>
+      <c r="F317" t="b">
+        <v>1</v>
+      </c>
+      <c r="G317" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>10.1007/s11426-026-3904-1 | 20 bar | H2/CO2 3 | 6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Figure 1A/B and text, CuZnZr, 230 °C</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>874.563</v>
+      </c>
+      <c r="D318" t="n">
+        <v>880.03</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1194.81</v>
+      </c>
+      <c r="F318" t="b">
+        <v>1</v>
+      </c>
+      <c r="G318" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.69 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Tables 5-6, FB, 220 °C</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>1119</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1682</v>
+      </c>
+      <c r="E319" t="n">
+        <v>20219.6</v>
+      </c>
+      <c r="F319" t="b">
+        <v>1</v>
+      </c>
+      <c r="G319" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.69 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Tables 5-6, FB, 235 °C</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>1136.51</v>
+      </c>
+      <c r="D320" t="n">
+        <v>2146.55</v>
+      </c>
+      <c r="E320" t="n">
+        <v>39606.4</v>
+      </c>
+      <c r="F320" t="b">
+        <v>1</v>
+      </c>
+      <c r="G320" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.69 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Tables 5-6, FB, 250 °C</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>1211.32</v>
+      </c>
+      <c r="D321" t="n">
+        <v>3077.01</v>
+      </c>
+      <c r="E321" t="n">
+        <v>78548.10000000001</v>
+      </c>
+      <c r="F321" t="b">
+        <v>1</v>
+      </c>
+      <c r="G321" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Table 4, 220 °C</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>1119.02</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1637.83</v>
+      </c>
+      <c r="E322" t="n">
+        <v>12562.1</v>
+      </c>
+      <c r="F322" t="b">
+        <v>1</v>
+      </c>
+      <c r="G322" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Table 4, 225 °C</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>1107.67</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1757.45</v>
+      </c>
+      <c r="E323" t="n">
+        <v>16183.3</v>
+      </c>
+      <c r="F323" t="b">
+        <v>1</v>
+      </c>
+      <c r="G323" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Table 4, 230 °C</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>1102.84</v>
+      </c>
+      <c r="D324" t="n">
+        <v>1905.86</v>
+      </c>
+      <c r="E324" t="n">
+        <v>20789.5</v>
+      </c>
+      <c r="F324" t="b">
+        <v>1</v>
+      </c>
+      <c r="G324" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Table 4, 235 °C</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>1109.62</v>
+      </c>
+      <c r="D325" t="n">
+        <v>2095.63</v>
+      </c>
+      <c r="E325" t="n">
+        <v>27106.1</v>
+      </c>
+      <c r="F325" t="b">
+        <v>1</v>
+      </c>
+      <c r="G325" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Table 4, 240 °C</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>1132.94</v>
+      </c>
+      <c r="D326" t="n">
+        <v>2351.75</v>
+      </c>
+      <c r="E326" t="n">
+        <v>41356.7</v>
+      </c>
+      <c r="F326" t="b">
+        <v>1</v>
+      </c>
+      <c r="G326" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Table 4, 245 °C</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>1161.5</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2664.56</v>
+      </c>
+      <c r="E327" t="n">
+        <v>57195.1</v>
+      </c>
+      <c r="F327" t="b">
+        <v>1</v>
+      </c>
+      <c r="G327" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Table 4, 250 °C</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>1166.77</v>
+      </c>
+      <c r="D328" t="n">
+        <v>3018.33</v>
+      </c>
+      <c r="E328" t="n">
+        <v>59992.5</v>
+      </c>
+      <c r="F328" t="b">
+        <v>1</v>
+      </c>
+      <c r="G328" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Table 4, 255 °C</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>1193.09</v>
+      </c>
+      <c r="D329" t="n">
+        <v>3492.98</v>
+      </c>
+      <c r="E329" t="n">
+        <v>77406.89999999999</v>
+      </c>
+      <c r="F329" t="b">
+        <v>1</v>
+      </c>
+      <c r="G329" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Table 4, 260 °C</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>1214.73</v>
+      </c>
+      <c r="D330" t="n">
+        <v>4073.57</v>
+      </c>
+      <c r="E330" t="n">
+        <v>93159.89999999999</v>
+      </c>
+      <c r="F330" t="b">
+        <v>1</v>
+      </c>
+      <c r="G330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Table 4, 265 °C</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>1247.63</v>
+      </c>
+      <c r="D331" t="n">
+        <v>4802.38</v>
+      </c>
+      <c r="E331" t="n">
+        <v>115056</v>
+      </c>
+      <c r="F331" t="b">
+        <v>1</v>
+      </c>
+      <c r="G331" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Table 4, 270 °C</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>1273.33</v>
+      </c>
+      <c r="D332" t="n">
+        <v>5690.5</v>
+      </c>
+      <c r="E332" t="n">
+        <v>136356</v>
+      </c>
+      <c r="F332" t="b">
+        <v>1</v>
+      </c>
+      <c r="G332" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 2.7 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Table 4, 275 °C</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>1297.57</v>
+      </c>
+      <c r="D333" t="n">
+        <v>6776.54</v>
+      </c>
+      <c r="E333" t="n">
+        <v>156249</v>
+      </c>
+      <c r="F333" t="b">
+        <v>1</v>
+      </c>
+      <c r="G333" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 8.3 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Tables 5-6, BFB, 220 °C</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>1039.41</v>
+      </c>
+      <c r="D334" t="n">
+        <v>1594.73</v>
+      </c>
+      <c r="E334" t="n">
+        <v>19672.3</v>
+      </c>
+      <c r="F334" t="b">
+        <v>1</v>
+      </c>
+      <c r="G334" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 8.3 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Tables 5-6, BFB, 235 °C</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>1047.54</v>
+      </c>
+      <c r="D335" t="n">
+        <v>2049.17</v>
+      </c>
+      <c r="E335" t="n">
+        <v>44950.3</v>
+      </c>
+      <c r="F335" t="b">
+        <v>1</v>
+      </c>
+      <c r="G335" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>10.1016/j.cej.2025.170755 | 3 bar | H2/CO2 3.25 | 8.3 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Tables 5-6, BFB, 250 °C</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>1061.64</v>
+      </c>
+      <c r="D336" t="n">
+        <v>2924.09</v>
+      </c>
+      <c r="E336" t="n">
+        <v>80979.2</v>
+      </c>
+      <c r="F336" t="b">
+        <v>1</v>
+      </c>
+      <c r="G336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Fig 3a text, 280 °C, CZAM-LDH</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>863.059</v>
+      </c>
+      <c r="D337" t="n">
+        <v>894.617</v>
+      </c>
+      <c r="E337" t="n">
+        <v>1349.81</v>
+      </c>
+      <c r="F337" t="b">
+        <v>1</v>
+      </c>
+      <c r="G337" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Fig S7 text comparison, 260 °C, CZAM-LDH+p-PDVB</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>862.625</v>
+      </c>
+      <c r="D338" t="n">
+        <v>878.616</v>
+      </c>
+      <c r="E338" t="n">
+        <v>1191.42</v>
+      </c>
+      <c r="F338" t="b">
+        <v>1</v>
+      </c>
+      <c r="G338" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 4</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>886.824</v>
+      </c>
+      <c r="D339" t="n">
+        <v>889.518</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1062.52</v>
+      </c>
+      <c r="F339" t="b">
+        <v>0</v>
+      </c>
+      <c r="G339" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 5</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>868.998</v>
+      </c>
+      <c r="D340" t="n">
+        <v>870.8680000000001</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1117.69</v>
+      </c>
+      <c r="F340" t="b">
+        <v>1</v>
+      </c>
+      <c r="G340" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 20</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>867.063</v>
+      </c>
+      <c r="D341" t="n">
+        <v>877.576</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1234.69</v>
+      </c>
+      <c r="F341" t="b">
+        <v>1</v>
+      </c>
+      <c r="G341" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 21</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>861.3579999999999</v>
+      </c>
+      <c r="D342" t="n">
+        <v>892.891</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1356.38</v>
+      </c>
+      <c r="F342" t="b">
+        <v>1</v>
+      </c>
+      <c r="G342" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 22</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>883.636</v>
+      </c>
+      <c r="D343" t="n">
+        <v>888.996</v>
+      </c>
+      <c r="E343" t="n">
+        <v>1273.93</v>
+      </c>
+      <c r="F343" t="b">
+        <v>1</v>
+      </c>
+      <c r="G343" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 23</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>866.811</v>
+      </c>
+      <c r="D344" t="n">
+        <v>892.405</v>
+      </c>
+      <c r="E344" t="n">
+        <v>1377.86</v>
+      </c>
+      <c r="F344" t="b">
+        <v>1</v>
+      </c>
+      <c r="G344" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 36 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 24</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>888.277</v>
+      </c>
+      <c r="D345" t="n">
+        <v>895.1319999999999</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1154.58</v>
+      </c>
+      <c r="F345" t="b">
+        <v>1</v>
+      </c>
+      <c r="G345" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 36 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 25</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>868.979</v>
+      </c>
+      <c r="D346" t="n">
+        <v>890.509</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1229.9</v>
+      </c>
+      <c r="F346" t="b">
+        <v>1</v>
+      </c>
+      <c r="G346" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 50 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Text high pressure, 260 °C, CO2:H2=1:5, 5 MPa, CZAM-LDH+p-PDVB</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>872.297</v>
+      </c>
+      <c r="D347" t="n">
+        <v>873.802</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1052.95</v>
+      </c>
+      <c r="F347" t="b">
+        <v>1</v>
+      </c>
+      <c r="G347" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 50 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 3</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>870.821</v>
+      </c>
+      <c r="D348" t="n">
+        <v>881.1079999999999</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1146.15</v>
+      </c>
+      <c r="F348" t="b">
+        <v>1</v>
+      </c>
+      <c r="G348" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02654 | 30 bar | H2/CO2 3 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Text p4, ZnO/Cu at 240 °C</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>1674.99</v>
+      </c>
+      <c r="D349" t="n">
+        <v>2256.45</v>
+      </c>
+      <c r="E349" t="n">
+        <v>2256.45</v>
+      </c>
+      <c r="F349" t="b">
+        <v>0</v>
+      </c>
+      <c r="G349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02654 | 30 bar | H2/CO2 3 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Text p4, GaOx/Cu at 240 °C</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>1084.94</v>
+      </c>
+      <c r="D350" t="n">
+        <v>1327.45</v>
+      </c>
+      <c r="E350" t="n">
+        <v>1327.45</v>
+      </c>
+      <c r="F350" t="b">
+        <v>0</v>
+      </c>
+      <c r="G350" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02654 | 30 bar | H2/CO2 3 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Text p4, ZrO2/Cu (14:86) at 240 °C</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>956.138</v>
+      </c>
+      <c r="D351" t="n">
+        <v>993.721</v>
+      </c>
+      <c r="E351" t="n">
+        <v>1117.07</v>
+      </c>
+      <c r="F351" t="b">
+        <v>0</v>
+      </c>
+      <c r="G351" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02654 | 30 bar | H2/CO2 3 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Abstract / Section 3.1, ZrO2/Cu (14:86) at 280 °C</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>872.288</v>
+      </c>
+      <c r="D352" t="n">
+        <v>894.731</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1710.12</v>
+      </c>
+      <c r="F352" t="b">
+        <v>1</v>
+      </c>
+      <c r="G352" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02654 | 30 bar | H2/CO2 3 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Section 3.1, alkali-treated malachite-derived catalyst at 300 °C</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>873.9</v>
+      </c>
+      <c r="D353" t="n">
+        <v>927.109</v>
+      </c>
+      <c r="E353" t="n">
+        <v>2663.04</v>
+      </c>
+      <c r="F353" t="b">
+        <v>1</v>
+      </c>
+      <c r="G353" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Figure 2a, Pd/ZrO2</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>1319.78</v>
+      </c>
+      <c r="D354" t="n">
+        <v>1635.15</v>
+      </c>
+      <c r="E354" t="n">
+        <v>9449.92</v>
+      </c>
+      <c r="F354" t="b">
+        <v>0</v>
+      </c>
+      <c r="G354" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Figure 2a, Pd/1In2O3/ZrO2</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>925.77</v>
+      </c>
+      <c r="D355" t="n">
+        <v>993.3200000000001</v>
+      </c>
+      <c r="E355" t="n">
+        <v>4265.53</v>
+      </c>
+      <c r="F355" t="b">
+        <v>1</v>
+      </c>
+      <c r="G355" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Figure 2a, Pd/5In2O3/ZrO2</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>968.097</v>
+      </c>
+      <c r="D356" t="n">
+        <v>1178.17</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1262.59</v>
+      </c>
+      <c r="F356" t="b">
+        <v>1</v>
+      </c>
+      <c r="G356" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Figure 2a, Pd/10In2O3/ZrO2</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>1006.7</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1152.87</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1152.87</v>
+      </c>
+      <c r="F357" t="b">
+        <v>0</v>
+      </c>
+      <c r="G357" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Figure 2a, Pd/15In2O3/ZrO2</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>1145.29</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1431.64</v>
+      </c>
+      <c r="E358" t="n">
+        <v>1431.64</v>
+      </c>
+      <c r="F358" t="b">
+        <v>0</v>
+      </c>
+      <c r="G358" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Figure 2b, 10In2O3/ZrO2</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>1327.83</v>
+      </c>
+      <c r="D359" t="n">
+        <v>1792.84</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1792.84</v>
+      </c>
+      <c r="F359" t="b">
+        <v>0</v>
+      </c>
+      <c r="G359" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Figure 2b, 10In2O3/SiO2</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>2047.43</v>
+      </c>
+      <c r="D360" t="n">
+        <v>6591.47</v>
+      </c>
+      <c r="E360" t="n">
+        <v>6591.47</v>
+      </c>
+      <c r="F360" t="b">
+        <v>0</v>
+      </c>
+      <c r="G360" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Figure 2b, Pd/10In2O3/SiO2</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>2250.18</v>
+      </c>
+      <c r="D361" t="n">
+        <v>3037.43</v>
+      </c>
+      <c r="E361" t="n">
+        <v>3037.43</v>
+      </c>
+      <c r="F361" t="b">
+        <v>0</v>
+      </c>
+      <c r="G361" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Figure 2c/text, Pd/10In2O3/ZrO2, 100 h</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>931.645</v>
+      </c>
+      <c r="D362" t="n">
+        <v>1029.37</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1248.5</v>
+      </c>
+      <c r="F362" t="b">
+        <v>1</v>
+      </c>
+      <c r="G362" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02971 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Figure 1a,b, CZA-N2, 3 MPa, 12000 mL gcat-1 h-1</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>858.995</v>
+      </c>
+      <c r="D363" t="n">
+        <v>878.442</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1455.7</v>
+      </c>
+      <c r="F363" t="b">
+        <v>1</v>
+      </c>
+      <c r="G363" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02971 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Figure 1a,b, CZA-0.1GC, 3 MPa, 12000 mL gcat-1 h-1</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>857.394</v>
+      </c>
+      <c r="D364" t="n">
+        <v>876.3920000000001</v>
+      </c>
+      <c r="E364" t="n">
+        <v>1338.48</v>
+      </c>
+      <c r="F364" t="b">
+        <v>1</v>
+      </c>
+      <c r="G364" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02971 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Figure 1a,b, CZA-0.1AC, 3 MPa, 12000 mL gcat-1 h-1</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>855.646</v>
+      </c>
+      <c r="D365" t="n">
+        <v>875.845</v>
+      </c>
+      <c r="E365" t="n">
+        <v>1290.38</v>
+      </c>
+      <c r="F365" t="b">
+        <v>1</v>
+      </c>
+      <c r="G365" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02971 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Figure 1a,b, CZA-0.1CNT, 3 MPa, 12000 mL gcat-1 h-1</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>859.197</v>
+      </c>
+      <c r="D366" t="n">
+        <v>877.604</v>
+      </c>
+      <c r="E366" t="n">
+        <v>1299.95</v>
+      </c>
+      <c r="F366" t="b">
+        <v>1</v>
+      </c>
+      <c r="G366" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02971 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SI Table S1 row 1</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>858.1319999999999</v>
+      </c>
+      <c r="D367" t="n">
+        <v>877.712</v>
+      </c>
+      <c r="E367" t="n">
+        <v>1392.99</v>
+      </c>
+      <c r="F367" t="b">
+        <v>1</v>
+      </c>
+      <c r="G367" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02971 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SI Table S1 row 3</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>861.881</v>
+      </c>
+      <c r="D368" t="n">
+        <v>877.754</v>
+      </c>
+      <c r="E368" t="n">
+        <v>1298.51</v>
+      </c>
+      <c r="F368" t="b">
+        <v>1</v>
+      </c>
+      <c r="G368" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02971 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SI Table S1 row 4</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>870.202</v>
+      </c>
+      <c r="D369" t="n">
+        <v>878.711</v>
+      </c>
+      <c r="E369" t="n">
+        <v>1264.57</v>
+      </c>
+      <c r="F369" t="b">
+        <v>1</v>
+      </c>
+      <c r="G369" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02971 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SI Table S2 row 2</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>860.578</v>
+      </c>
+      <c r="D370" t="n">
+        <v>878.169</v>
+      </c>
+      <c r="E370" t="n">
+        <v>1405.23</v>
+      </c>
+      <c r="F370" t="b">
+        <v>1</v>
+      </c>
+      <c r="G370" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01275 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Figure 1d/text, 11ZnO/TiO2, 5.0 MPa</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>980.342</v>
+      </c>
+      <c r="D371" t="n">
+        <v>1150.49</v>
+      </c>
+      <c r="E371" t="n">
+        <v>1150.49</v>
+      </c>
+      <c r="F371" t="b">
+        <v>0</v>
+      </c>
+      <c r="G371" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01275 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Figure 1d/text, 0.6ReOx11ZnO/TiO2, 5.0 MPa</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>936.894</v>
+      </c>
+      <c r="D372" t="n">
+        <v>961.453</v>
+      </c>
+      <c r="E372" t="n">
+        <v>1136.09</v>
+      </c>
+      <c r="F372" t="b">
+        <v>1</v>
+      </c>
+      <c r="G372" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01304 | 45 bar | H2/CO2 3 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Fig 7/text, h-ZrO2@Cu1.3ZnAl1.6-LDH, 250 °C, STY per g Cu</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>864.311</v>
+      </c>
+      <c r="D373" t="n">
+        <v>866.971</v>
+      </c>
+      <c r="E373" t="n">
+        <v>1183.99</v>
+      </c>
+      <c r="F373" t="b">
+        <v>1</v>
+      </c>
+      <c r="G373" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01304 | 45 bar | H2/CO2 3 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Fig 7/text, commercial catalyst, 250 °C, STY per g Cu</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>860.383</v>
+      </c>
+      <c r="D374" t="n">
+        <v>866.686</v>
+      </c>
+      <c r="E374" t="n">
+        <v>1279.21</v>
+      </c>
+      <c r="F374" t="b">
+        <v>1</v>
+      </c>
+      <c r="G374" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01304 | 45 bar | H2/CO2 3 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Fig 8, Cu1.3ZnAl-LDH, 250 °C, STY per g Cu</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>864.77</v>
+      </c>
+      <c r="D375" t="n">
+        <v>867.5119999999999</v>
+      </c>
+      <c r="E375" t="n">
+        <v>1346.5</v>
+      </c>
+      <c r="F375" t="b">
+        <v>1</v>
+      </c>
+      <c r="G375" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 120 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Text p3, 1 bar at 200 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>2032.01</v>
+      </c>
+      <c r="D376" t="n">
+        <v>2806.65</v>
+      </c>
+      <c r="E376" t="n">
+        <v>2806.65</v>
+      </c>
+      <c r="F376" t="b">
+        <v>1</v>
+      </c>
+      <c r="G376" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 120 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SI Table S9, 180 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>2769.58</v>
+      </c>
+      <c r="D377" t="n">
+        <v>3382.33</v>
+      </c>
+      <c r="E377" t="n">
+        <v>3382.33</v>
+      </c>
+      <c r="F377" t="b">
+        <v>0</v>
+      </c>
+      <c r="G377" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 120 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SI Table S9, 220 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>1221.64</v>
+      </c>
+      <c r="D378" t="n">
+        <v>2356.36</v>
+      </c>
+      <c r="E378" t="n">
+        <v>2356.36</v>
+      </c>
+      <c r="F378" t="b">
+        <v>1</v>
+      </c>
+      <c r="G378" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 120 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SI Table S9, 230 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>1088.25</v>
+      </c>
+      <c r="D379" t="n">
+        <v>2978.63</v>
+      </c>
+      <c r="E379" t="n">
+        <v>2978.63</v>
+      </c>
+      <c r="F379" t="b">
+        <v>1</v>
+      </c>
+      <c r="G379" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 120 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SI Table S9, 240 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>1011.72</v>
+      </c>
+      <c r="D380" t="n">
+        <v>4275.04</v>
+      </c>
+      <c r="E380" t="n">
+        <v>4275.04</v>
+      </c>
+      <c r="F380" t="b">
+        <v>1</v>
+      </c>
+      <c r="G380" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 120 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SI Table S9, 260 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>918.809</v>
+      </c>
+      <c r="D381" t="n">
+        <v>10585.6</v>
+      </c>
+      <c r="E381" t="n">
+        <v>11627.7</v>
+      </c>
+      <c r="F381" t="b">
+        <v>1</v>
+      </c>
+      <c r="G381" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 120 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SI Table S9, 280 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>886.03</v>
+      </c>
+      <c r="D382" t="n">
+        <v>24064.2</v>
+      </c>
+      <c r="E382" t="n">
+        <v>37220.1</v>
+      </c>
+      <c r="F382" t="b">
+        <v>1</v>
+      </c>
+      <c r="G382" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Text p3, 1 bar at 200 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>1719.7</v>
+      </c>
+      <c r="D383" t="n">
+        <v>2068.24</v>
+      </c>
+      <c r="E383" t="n">
+        <v>2068.24</v>
+      </c>
+      <c r="F383" t="b">
+        <v>1</v>
+      </c>
+      <c r="G383" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SI Table S9, 180 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>1827.11</v>
+      </c>
+      <c r="D384" t="n">
+        <v>2061.97</v>
+      </c>
+      <c r="E384" t="n">
+        <v>2061.97</v>
+      </c>
+      <c r="F384" t="b">
+        <v>1</v>
+      </c>
+      <c r="G384" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SI Table S9, 220 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>1114.74</v>
+      </c>
+      <c r="D385" t="n">
+        <v>1828.45</v>
+      </c>
+      <c r="E385" t="n">
+        <v>1828.45</v>
+      </c>
+      <c r="F385" t="b">
+        <v>1</v>
+      </c>
+      <c r="G385" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SI Table S9, 230 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>1048.83</v>
+      </c>
+      <c r="D386" t="n">
+        <v>2074.86</v>
+      </c>
+      <c r="E386" t="n">
+        <v>2074.86</v>
+      </c>
+      <c r="F386" t="b">
+        <v>1</v>
+      </c>
+      <c r="G386" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SI Table S9, 240 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>1066.76</v>
+      </c>
+      <c r="D387" t="n">
+        <v>2547.69</v>
+      </c>
+      <c r="E387" t="n">
+        <v>2547.69</v>
+      </c>
+      <c r="F387" t="b">
+        <v>1</v>
+      </c>
+      <c r="G387" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SI Table S9, 260 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>962.566</v>
+      </c>
+      <c r="D388" t="n">
+        <v>5128.3</v>
+      </c>
+      <c r="E388" t="n">
+        <v>5128.3</v>
+      </c>
+      <c r="F388" t="b">
+        <v>1</v>
+      </c>
+      <c r="G388" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SI Table S9, 280 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>936.413</v>
+      </c>
+      <c r="D389" t="n">
+        <v>11369.9</v>
+      </c>
+      <c r="E389" t="n">
+        <v>11369.9</v>
+      </c>
+      <c r="F389" t="b">
+        <v>1</v>
+      </c>
+      <c r="G389" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>SI Table S11, 200 °C, 1 bar, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>1650.23</v>
+      </c>
+      <c r="D390" t="n">
+        <v>2503.78</v>
+      </c>
+      <c r="E390" t="n">
+        <v>2503.78</v>
+      </c>
+      <c r="F390" t="b">
+        <v>1</v>
+      </c>
+      <c r="G390" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SI Table S11, 260 °C, 1 bar, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>951.901</v>
+      </c>
+      <c r="D391" t="n">
+        <v>10635</v>
+      </c>
+      <c r="E391" t="n">
+        <v>21631.7</v>
+      </c>
+      <c r="F391" t="b">
+        <v>1</v>
+      </c>
+      <c r="G391" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 10 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SI Table S11, 200 °C, 10 bar, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>1102.33</v>
+      </c>
+      <c r="D392" t="n">
+        <v>1184.4</v>
+      </c>
+      <c r="E392" t="n">
+        <v>1203.39</v>
+      </c>
+      <c r="F392" t="b">
+        <v>0</v>
+      </c>
+      <c r="G392" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 10 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>SI Table S11, 200 °C, 10 bar, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>1236.41</v>
+      </c>
+      <c r="D393" t="n">
+        <v>1304.67</v>
+      </c>
+      <c r="E393" t="n">
+        <v>1304.67</v>
+      </c>
+      <c r="F393" t="b">
+        <v>0</v>
+      </c>
+      <c r="G393" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 10 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>SI Table S11, 260 °C, 10 bar, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>889.3099999999999</v>
+      </c>
+      <c r="D394" t="n">
+        <v>1021.69</v>
+      </c>
+      <c r="E394" t="n">
+        <v>2202.44</v>
+      </c>
+      <c r="F394" t="b">
+        <v>1</v>
+      </c>
+      <c r="G394" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 10 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>SI Table S11, 260 °C, 10 bar, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>955.345</v>
+      </c>
+      <c r="D395" t="n">
+        <v>1025.35</v>
+      </c>
+      <c r="E395" t="n">
+        <v>1367.59</v>
+      </c>
+      <c r="F395" t="b">
+        <v>1</v>
+      </c>
+      <c r="G395" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 2.5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>SI Table S11, 200 °C, 2.5 bar, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>1937.43</v>
+      </c>
+      <c r="D396" t="n">
+        <v>2421.59</v>
+      </c>
+      <c r="E396" t="n">
+        <v>2421.59</v>
+      </c>
+      <c r="F396" t="b">
+        <v>1</v>
+      </c>
+      <c r="G396" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 2.5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SI Table S11, 200 °C, 2.5 bar, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>2374.51</v>
+      </c>
+      <c r="D397" t="n">
+        <v>2678.34</v>
+      </c>
+      <c r="E397" t="n">
+        <v>2678.34</v>
+      </c>
+      <c r="F397" t="b">
+        <v>1</v>
+      </c>
+      <c r="G397" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 2.5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>SI Table S11, 260 °C, 2.5 bar, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>1026.41</v>
+      </c>
+      <c r="D398" t="n">
+        <v>6104.04</v>
+      </c>
+      <c r="E398" t="n">
+        <v>8523.530000000001</v>
+      </c>
+      <c r="F398" t="b">
+        <v>1</v>
+      </c>
+      <c r="G398" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 2.5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>SI Table S11, 260 °C, 2.5 bar, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D399" t="n">
+        <v>4063.14</v>
+      </c>
+      <c r="E399" t="n">
+        <v>4063.14</v>
+      </c>
+      <c r="F399" t="b">
+        <v>1</v>
+      </c>
+      <c r="G399" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 15 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Text p3, constant methanol production rate at 240 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>984.115</v>
+      </c>
+      <c r="D400" t="n">
+        <v>1031.5</v>
+      </c>
+      <c r="E400" t="n">
+        <v>1040.25</v>
+      </c>
+      <c r="F400" t="b">
+        <v>0</v>
+      </c>
+      <c r="G400" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 15 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SI Table S5, CuZn-NH4HCO3, W/F 15000.0</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>881.388</v>
+      </c>
+      <c r="D401" t="n">
+        <v>886.075</v>
+      </c>
+      <c r="E401" t="n">
+        <v>1198.34</v>
+      </c>
+      <c r="F401" t="b">
+        <v>1</v>
+      </c>
+      <c r="G401" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 15 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SI Table S5, CuZn-NH4OH-0.25, W/F 15000.0</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>920.2859999999999</v>
+      </c>
+      <c r="D402" t="n">
+        <v>935.018</v>
+      </c>
+      <c r="E402" t="n">
+        <v>1037.09</v>
+      </c>
+      <c r="F402" t="b">
+        <v>0</v>
+      </c>
+      <c r="G402" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 22.2 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Text p3, constant methanol production rate at 240 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>887.7380000000001</v>
+      </c>
+      <c r="D403" t="n">
+        <v>894.1799999999999</v>
+      </c>
+      <c r="E403" t="n">
+        <v>1150.65</v>
+      </c>
+      <c r="F403" t="b">
+        <v>1</v>
+      </c>
+      <c r="G403" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 22.2 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SI Table S5, CuZn-NaOH-0.5, W/F 22222.2</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>923.09</v>
+      </c>
+      <c r="D404" t="n">
+        <v>940.14</v>
+      </c>
+      <c r="E404" t="n">
+        <v>1023.12</v>
+      </c>
+      <c r="F404" t="b">
+        <v>0</v>
+      </c>
+      <c r="G404" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 22.2 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SI Table S5, CuZn-NH4OH-0.25, W/F 22222.2</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>935.715</v>
+      </c>
+      <c r="D405" t="n">
+        <v>958.385</v>
+      </c>
+      <c r="E405" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="F405" t="b">
+        <v>0</v>
+      </c>
+      <c r="G405" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Text p3, iso-conversion at 240 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>1036.91</v>
+      </c>
+      <c r="D406" t="n">
+        <v>1054.96</v>
+      </c>
+      <c r="E406" t="n">
+        <v>1107.78</v>
+      </c>
+      <c r="F406" t="b">
+        <v>0</v>
+      </c>
+      <c r="G406" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Text p3, iso-conversion at 240 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>888.167</v>
+      </c>
+      <c r="D407" t="n">
+        <v>894.772</v>
+      </c>
+      <c r="E407" t="n">
+        <v>1147.03</v>
+      </c>
+      <c r="F407" t="b">
+        <v>1</v>
+      </c>
+      <c r="G407" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SI Table S4, 220 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>918.806</v>
+      </c>
+      <c r="D408" t="n">
+        <v>929.9829999999999</v>
+      </c>
+      <c r="E408" t="n">
+        <v>1029.5</v>
+      </c>
+      <c r="F408" t="b">
+        <v>0</v>
+      </c>
+      <c r="G408" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>SI Table S4, 220 °C, CuZn-NaOH-1.0</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>1003.66</v>
+      </c>
+      <c r="D409" t="n">
+        <v>1054.04</v>
+      </c>
+      <c r="E409" t="n">
+        <v>1066.39</v>
+      </c>
+      <c r="F409" t="b">
+        <v>0</v>
+      </c>
+      <c r="G409" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SI Table S4, 220 °C, CuZn-NaOH-0.5</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>967.729</v>
+      </c>
+      <c r="D410" t="n">
+        <v>997.196</v>
+      </c>
+      <c r="E410" t="n">
+        <v>1014.99</v>
+      </c>
+      <c r="F410" t="b">
+        <v>0</v>
+      </c>
+      <c r="G410" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SI Table S4, 220 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>1031.59</v>
+      </c>
+      <c r="D411" t="n">
+        <v>1063.89</v>
+      </c>
+      <c r="E411" t="n">
+        <v>1063.89</v>
+      </c>
+      <c r="F411" t="b">
+        <v>0</v>
+      </c>
+      <c r="G411" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>SI Table S4, 220 °C, CuZn-NH4OH-0.25</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>956.028</v>
+      </c>
+      <c r="D412" t="n">
+        <v>979.633</v>
+      </c>
+      <c r="E412" t="n">
+        <v>1025.72</v>
+      </c>
+      <c r="F412" t="b">
+        <v>0</v>
+      </c>
+      <c r="G412" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>SI Table S4, 240 °C, CuZn-NaOH-1.0</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>958.153</v>
+      </c>
+      <c r="D413" t="n">
+        <v>995.127</v>
+      </c>
+      <c r="E413" t="n">
+        <v>1072.32</v>
+      </c>
+      <c r="F413" t="b">
+        <v>0</v>
+      </c>
+      <c r="G413" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SI Table S4, 240 °C, CuZn-NaOH-0.5</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>931.954</v>
+      </c>
+      <c r="D414" t="n">
+        <v>953.6609999999999</v>
+      </c>
+      <c r="E414" t="n">
+        <v>1024.58</v>
+      </c>
+      <c r="F414" t="b">
+        <v>0</v>
+      </c>
+      <c r="G414" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>SI Table S4, 240 °C, CuZn-NH4OH-0.25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>924.7859999999999</v>
+      </c>
+      <c r="D415" t="n">
+        <v>943.231</v>
+      </c>
+      <c r="E415" t="n">
+        <v>1055.37</v>
+      </c>
+      <c r="F415" t="b">
+        <v>0</v>
+      </c>
+      <c r="G415" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SI Table S4, 260 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>871.578</v>
+      </c>
+      <c r="D416" t="n">
+        <v>900.59</v>
+      </c>
+      <c r="E416" t="n">
+        <v>1431.95</v>
+      </c>
+      <c r="F416" t="b">
+        <v>1</v>
+      </c>
+      <c r="G416" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>SI Table S4, 260 °C, CuZn-NaOH-1.0</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>922.883</v>
+      </c>
+      <c r="D417" t="n">
+        <v>948.266</v>
+      </c>
+      <c r="E417" t="n">
+        <v>1128.95</v>
+      </c>
+      <c r="F417" t="b">
+        <v>0</v>
+      </c>
+      <c r="G417" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>SI Table S4, 260 °C, CuZn-NaOH-0.5</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>908.579</v>
+      </c>
+      <c r="D418" t="n">
+        <v>926.277</v>
+      </c>
+      <c r="E418" t="n">
+        <v>1091.99</v>
+      </c>
+      <c r="F418" t="b">
+        <v>0</v>
+      </c>
+      <c r="G418" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>SI Table S4, 260 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>985.807</v>
+      </c>
+      <c r="D419" t="n">
+        <v>1064.28</v>
+      </c>
+      <c r="E419" t="n">
+        <v>1064.28</v>
+      </c>
+      <c r="F419" t="b">
+        <v>0</v>
+      </c>
+      <c r="G419" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SI Table S4, 260 °C, CuZn-NH4OH-0.25</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>899.254</v>
+      </c>
+      <c r="D420" t="n">
+        <v>913.067</v>
+      </c>
+      <c r="E420" t="n">
+        <v>1174.3</v>
+      </c>
+      <c r="F420" t="b">
+        <v>0</v>
+      </c>
+      <c r="G420" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>SI Table S4, 280 °C, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>866.99</v>
+      </c>
+      <c r="D421" t="n">
+        <v>935.7329999999999</v>
+      </c>
+      <c r="E421" t="n">
+        <v>2030.71</v>
+      </c>
+      <c r="F421" t="b">
+        <v>1</v>
+      </c>
+      <c r="G421" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>SI Table S4, 280 °C, CuZn-NaOH-1.0</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>899.461</v>
+      </c>
+      <c r="D422" t="n">
+        <v>935.7329999999999</v>
+      </c>
+      <c r="E422" t="n">
+        <v>1344.04</v>
+      </c>
+      <c r="F422" t="b">
+        <v>0</v>
+      </c>
+      <c r="G422" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>SI Table S4, 280 °C, CuZn-NaOH-0.5</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>891.375</v>
+      </c>
+      <c r="D423" t="n">
+        <v>934.901</v>
+      </c>
+      <c r="E423" t="n">
+        <v>1320.84</v>
+      </c>
+      <c r="F423" t="b">
+        <v>1</v>
+      </c>
+      <c r="G423" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>SI Table S4, 280 °C, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>959.833</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1041.44</v>
+      </c>
+      <c r="E424" t="n">
+        <v>1081.82</v>
+      </c>
+      <c r="F424" t="b">
+        <v>0</v>
+      </c>
+      <c r="G424" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>SI Table S4, 280 °C, CuZn-NH4OH-0.25</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>882.485</v>
+      </c>
+      <c r="D425" t="n">
+        <v>934.901</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1481.83</v>
+      </c>
+      <c r="F425" t="b">
+        <v>1</v>
+      </c>
+      <c r="G425" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 7.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SI Table S5, CuZn-NH4HCO3, W/F 7500.0</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>877.072</v>
+      </c>
+      <c r="D426" t="n">
+        <v>888.891</v>
+      </c>
+      <c r="E426" t="n">
+        <v>1261.25</v>
+      </c>
+      <c r="F426" t="b">
+        <v>1</v>
+      </c>
+      <c r="G426" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 7.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>SI Table S5, CuZn-NaOH-0.25, W/F 7500.0</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>949.5359999999999</v>
+      </c>
+      <c r="D427" t="n">
+        <v>974.294</v>
+      </c>
+      <c r="E427" t="n">
+        <v>1014.64</v>
+      </c>
+      <c r="F427" t="b">
+        <v>0</v>
+      </c>
+      <c r="G427" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 7.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>SI Table S5, CuZn-NH4OH-0.25, W/F 7500.0</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>904.266</v>
+      </c>
+      <c r="D428" t="n">
+        <v>912.492</v>
+      </c>
+      <c r="E428" t="n">
+        <v>1073.39</v>
+      </c>
+      <c r="F428" t="b">
+        <v>0</v>
+      </c>
+      <c r="G428" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 40 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>SI Table S16, 220 °C, 40 bar</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>1038.07</v>
+      </c>
+      <c r="D429" t="n">
+        <v>1061.17</v>
+      </c>
+      <c r="E429" t="n">
+        <v>1061.17</v>
+      </c>
+      <c r="F429" t="b">
+        <v>0</v>
+      </c>
+      <c r="G429" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 40 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>SI Table S16, 240 °C, 40 bar</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>998.403</v>
+      </c>
+      <c r="D430" t="n">
+        <v>1033.33</v>
+      </c>
+      <c r="E430" t="n">
+        <v>1033.33</v>
+      </c>
+      <c r="F430" t="b">
+        <v>1</v>
+      </c>
+      <c r="G430" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 40 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>SI Table S16, 260 °C, 40 bar</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>978.024</v>
+      </c>
+      <c r="D431" t="n">
+        <v>1034.93</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1034.93</v>
+      </c>
+      <c r="F431" t="b">
+        <v>1</v>
+      </c>
+      <c r="G431" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 40 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>SI Table S16, 280 °C, 40 bar</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>956.979</v>
+      </c>
+      <c r="D432" t="n">
+        <v>1023.31</v>
+      </c>
+      <c r="E432" t="n">
+        <v>1041.99</v>
+      </c>
+      <c r="F432" t="b">
+        <v>1</v>
+      </c>
+      <c r="G432" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>SI Table S11, 200 °C, 5 bar, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>1319.27</v>
+      </c>
+      <c r="D433" t="n">
+        <v>1516.41</v>
+      </c>
+      <c r="E433" t="n">
+        <v>1516.41</v>
+      </c>
+      <c r="F433" t="b">
+        <v>1</v>
+      </c>
+      <c r="G433" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>SI Table S11, 200 °C, 5 bar, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>1557.17</v>
+      </c>
+      <c r="D434" t="n">
+        <v>1692.21</v>
+      </c>
+      <c r="E434" t="n">
+        <v>1692.21</v>
+      </c>
+      <c r="F434" t="b">
+        <v>0</v>
+      </c>
+      <c r="G434" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>SI Table S11, 260 °C, 5 bar, CuZn-NH4HCO3</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>931.7329999999999</v>
+      </c>
+      <c r="D435" t="n">
+        <v>1621.1</v>
+      </c>
+      <c r="E435" t="n">
+        <v>3961.96</v>
+      </c>
+      <c r="F435" t="b">
+        <v>1</v>
+      </c>
+      <c r="G435" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>SI Table S11, 260 °C, 5 bar, CuZn-NaOH-0.25</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>1034.77</v>
+      </c>
+      <c r="D436" t="n">
+        <v>1622.04</v>
+      </c>
+      <c r="E436" t="n">
+        <v>1921.84</v>
+      </c>
+      <c r="F436" t="b">
+        <v>1</v>
+      </c>
+      <c r="G436" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Fig 3e, Cu, 220 °C</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>1803.37</v>
+      </c>
+      <c r="D437" t="n">
+        <v>2106.04</v>
+      </c>
+      <c r="E437" t="n">
+        <v>2106.04</v>
+      </c>
+      <c r="F437" t="b">
+        <v>0</v>
+      </c>
+      <c r="G437" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Fig 3e, Cu, 230 °C</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>1483.85</v>
+      </c>
+      <c r="D438" t="n">
+        <v>1886.8</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1886.8</v>
+      </c>
+      <c r="F438" t="b">
+        <v>0</v>
+      </c>
+      <c r="G438" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Fig 3e, Cu, 240 °C</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>1258.44</v>
+      </c>
+      <c r="D439" t="n">
+        <v>1703.05</v>
+      </c>
+      <c r="E439" t="n">
+        <v>1703.05</v>
+      </c>
+      <c r="F439" t="b">
+        <v>0</v>
+      </c>
+      <c r="G439" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Fig 3e, Cu, 260 °C</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>1027.1</v>
+      </c>
+      <c r="D440" t="n">
+        <v>1170.04</v>
+      </c>
+      <c r="E440" t="n">
+        <v>1592.19</v>
+      </c>
+      <c r="F440" t="b">
+        <v>0</v>
+      </c>
+      <c r="G440" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Text/Fig 3c, Cu, 280 °C</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>928.348</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1019.43</v>
+      </c>
+      <c r="E441" t="n">
+        <v>1872.68</v>
+      </c>
+      <c r="F441" t="b">
+        <v>1</v>
+      </c>
+      <c r="G441" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuZn1.5, 220 °C</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>2735.2</v>
+      </c>
+      <c r="D442" t="n">
+        <v>3309.85</v>
+      </c>
+      <c r="E442" t="n">
+        <v>3309.85</v>
+      </c>
+      <c r="F442" t="b">
+        <v>0</v>
+      </c>
+      <c r="G442" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuZn1.5, 230 °C</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>1995.17</v>
+      </c>
+      <c r="D443" t="n">
+        <v>2564.44</v>
+      </c>
+      <c r="E443" t="n">
+        <v>2564.44</v>
+      </c>
+      <c r="F443" t="b">
+        <v>0</v>
+      </c>
+      <c r="G443" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuZn1.5, 240 °C</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>1822.12</v>
+      </c>
+      <c r="D444" t="n">
+        <v>2651.36</v>
+      </c>
+      <c r="E444" t="n">
+        <v>2651.36</v>
+      </c>
+      <c r="F444" t="b">
+        <v>0</v>
+      </c>
+      <c r="G444" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuZn1.5, 260 °C</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>1241.81</v>
+      </c>
+      <c r="D445" t="n">
+        <v>2068.05</v>
+      </c>
+      <c r="E445" t="n">
+        <v>2068.05</v>
+      </c>
+      <c r="F445" t="b">
+        <v>0</v>
+      </c>
+      <c r="G445" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Text/Fig 3c, CuZn1.5, 280 °C</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>1010.42</v>
+      </c>
+      <c r="D446" t="n">
+        <v>1162.13</v>
+      </c>
+      <c r="E446" t="n">
+        <v>1957.23</v>
+      </c>
+      <c r="F446" t="b">
+        <v>1</v>
+      </c>
+      <c r="G446" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuLa1.5, 220 °C</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>1677.64</v>
+      </c>
+      <c r="D447" t="n">
+        <v>2042.19</v>
+      </c>
+      <c r="E447" t="n">
+        <v>2042.19</v>
+      </c>
+      <c r="F447" t="b">
+        <v>0</v>
+      </c>
+      <c r="G447" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuLa1.5, 230 °C</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>1491.53</v>
+      </c>
+      <c r="D448" t="n">
+        <v>1942.56</v>
+      </c>
+      <c r="E448" t="n">
+        <v>1942.56</v>
+      </c>
+      <c r="F448" t="b">
+        <v>0</v>
+      </c>
+      <c r="G448" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuLa1.5, 240 °C</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>1263.4</v>
+      </c>
+      <c r="D449" t="n">
+        <v>1758.89</v>
+      </c>
+      <c r="E449" t="n">
+        <v>1758.89</v>
+      </c>
+      <c r="F449" t="b">
+        <v>0</v>
+      </c>
+      <c r="G449" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuLa1.5, 260 °C</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>1031.31</v>
+      </c>
+      <c r="D450" t="n">
+        <v>1175.13</v>
+      </c>
+      <c r="E450" t="n">
+        <v>1643.11</v>
+      </c>
+      <c r="F450" t="b">
+        <v>0</v>
+      </c>
+      <c r="G450" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Text/Fig 3c, CuLa1.5, 280 °C</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>929.401</v>
+      </c>
+      <c r="D451" t="n">
+        <v>1023.25</v>
+      </c>
+      <c r="E451" t="n">
+        <v>1921.97</v>
+      </c>
+      <c r="F451" t="b">
+        <v>1</v>
+      </c>
+      <c r="G451" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuIn1.5, 220 °C</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>1574.72</v>
+      </c>
+      <c r="D452" t="n">
+        <v>1900.99</v>
+      </c>
+      <c r="E452" t="n">
+        <v>1900.99</v>
+      </c>
+      <c r="F452" t="b">
+        <v>0</v>
+      </c>
+      <c r="G452" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuIn1.5, 230 °C</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>1371.88</v>
+      </c>
+      <c r="D453" t="n">
+        <v>1762.38</v>
+      </c>
+      <c r="E453" t="n">
+        <v>1762.38</v>
+      </c>
+      <c r="F453" t="b">
+        <v>0</v>
+      </c>
+      <c r="G453" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuIn1.5, 240 °C</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>1185.69</v>
+      </c>
+      <c r="D454" t="n">
+        <v>1618.5</v>
+      </c>
+      <c r="E454" t="n">
+        <v>1618.5</v>
+      </c>
+      <c r="F454" t="b">
+        <v>0</v>
+      </c>
+      <c r="G454" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Fig 3b, CuIn1.5, 260 °C</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>991.236</v>
+      </c>
+      <c r="D455" t="n">
+        <v>1073.64</v>
+      </c>
+      <c r="E455" t="n">
+        <v>1584.1</v>
+      </c>
+      <c r="F455" t="b">
+        <v>1</v>
+      </c>
+      <c r="G455" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Text/Fig 3c, CuIn1.5, 280 °C</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>909.551</v>
+      </c>
+      <c r="D456" t="n">
+        <v>1016.76</v>
+      </c>
+      <c r="E456" t="n">
+        <v>1979.71</v>
+      </c>
+      <c r="F456" t="b">
+        <v>1</v>
+      </c>
+      <c r="G456" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Fig 3e, CuGa1.5, 220 °C</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>1569.45</v>
+      </c>
+      <c r="D457" t="n">
+        <v>1905.88</v>
+      </c>
+      <c r="E457" t="n">
+        <v>1905.88</v>
+      </c>
+      <c r="F457" t="b">
+        <v>0</v>
+      </c>
+      <c r="G457" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Fig 3e, CuGa1.5, 230 °C</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>1327.1</v>
+      </c>
+      <c r="D458" t="n">
+        <v>1695.66</v>
+      </c>
+      <c r="E458" t="n">
+        <v>1695.66</v>
+      </c>
+      <c r="F458" t="b">
+        <v>0</v>
+      </c>
+      <c r="G458" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Fig 3e, CuGa1.5, 240 °C</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>1166.96</v>
+      </c>
+      <c r="D459" t="n">
+        <v>1593.18</v>
+      </c>
+      <c r="E459" t="n">
+        <v>1593.18</v>
+      </c>
+      <c r="F459" t="b">
+        <v>0</v>
+      </c>
+      <c r="G459" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Fig 3e, CuGa1.5, 260 °C</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>975.716</v>
+      </c>
+      <c r="D460" t="n">
+        <v>1039.48</v>
+      </c>
+      <c r="E460" t="n">
+        <v>1534.38</v>
+      </c>
+      <c r="F460" t="b">
+        <v>1</v>
+      </c>
+      <c r="G460" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Text/Fig 3c, CuGa1.5, 280 °C</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>898.162</v>
+      </c>
+      <c r="D461" t="n">
+        <v>1015.67</v>
+      </c>
+      <c r="E461" t="n">
+        <v>1970.22</v>
+      </c>
+      <c r="F461" t="b">
+        <v>1</v>
+      </c>
+      <c r="G461" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Fig 3e, CuGa2.5, 220 °C</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>1570.52</v>
+      </c>
+      <c r="D462" t="n">
+        <v>1947.34</v>
+      </c>
+      <c r="E462" t="n">
+        <v>1947.34</v>
+      </c>
+      <c r="F462" t="b">
+        <v>0</v>
+      </c>
+      <c r="G462" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Fig 3e, CuGa2.5, 230 °C</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>1290.98</v>
+      </c>
+      <c r="D463" t="n">
+        <v>1692.27</v>
+      </c>
+      <c r="E463" t="n">
+        <v>1692.27</v>
+      </c>
+      <c r="F463" t="b">
+        <v>0</v>
+      </c>
+      <c r="G463" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Fig 3e, CuGa2.5, 240 °C</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>1165.59</v>
+      </c>
+      <c r="D464" t="n">
+        <v>1617.99</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1617.99</v>
+      </c>
+      <c r="F464" t="b">
+        <v>0</v>
+      </c>
+      <c r="G464" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Fig 3e, CuGa2.5, 260 °C</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>969.252</v>
+      </c>
+      <c r="D465" t="n">
+        <v>1026</v>
+      </c>
+      <c r="E465" t="n">
+        <v>1558.1</v>
+      </c>
+      <c r="F465" t="b">
+        <v>1</v>
+      </c>
+      <c r="G465" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Text/Fig 3c, CuGa2.5, 280 °C</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>893.38</v>
+      </c>
+      <c r="D466" t="n">
+        <v>1015.51</v>
+      </c>
+      <c r="E466" t="n">
+        <v>2030.93</v>
+      </c>
+      <c r="F466" t="b">
+        <v>1</v>
+      </c>
+      <c r="G466" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Fig 3e, Cu-Ga2O3, 220 °C</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>2117.46</v>
+      </c>
+      <c r="D467" t="n">
+        <v>2943.56</v>
+      </c>
+      <c r="E467" t="n">
+        <v>2943.56</v>
+      </c>
+      <c r="F467" t="b">
+        <v>0</v>
+      </c>
+      <c r="G467" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Fig 3e, Cu-Ga2O3, 230 °C</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>1547.03</v>
+      </c>
+      <c r="D468" t="n">
+        <v>2343.54</v>
+      </c>
+      <c r="E468" t="n">
+        <v>2343.54</v>
+      </c>
+      <c r="F468" t="b">
+        <v>0</v>
+      </c>
+      <c r="G468" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Fig 3e, Cu-Ga2O3, 240 °C</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>1350.86</v>
+      </c>
+      <c r="D469" t="n">
+        <v>2219.42</v>
+      </c>
+      <c r="E469" t="n">
+        <v>2219.42</v>
+      </c>
+      <c r="F469" t="b">
+        <v>0</v>
+      </c>
+      <c r="G469" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Fig 3e, Cu-Ga2O3, 260 °C</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>1086.67</v>
+      </c>
+      <c r="D470" t="n">
+        <v>1407.49</v>
+      </c>
+      <c r="E470" t="n">
+        <v>2237.92</v>
+      </c>
+      <c r="F470" t="b">
+        <v>0</v>
+      </c>
+      <c r="G470" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Text/Fig 3d-e, Cu-Ga2O3, 280 °C</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>959.033</v>
+      </c>
+      <c r="D471" t="n">
+        <v>1022.47</v>
+      </c>
+      <c r="E471" t="n">
+        <v>2596.85</v>
+      </c>
+      <c r="F471" t="b">
+        <v>1</v>
+      </c>
+      <c r="G471" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>SI Table S8, Cu, 230 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>1297.21</v>
+      </c>
+      <c r="D472" t="n">
+        <v>1619.39</v>
+      </c>
+      <c r="E472" t="n">
+        <v>1619.39</v>
+      </c>
+      <c r="F472" t="b">
+        <v>0</v>
+      </c>
+      <c r="G472" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>SI Table S8, Cu, 240 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>1144.47</v>
+      </c>
+      <c r="D473" t="n">
+        <v>1506.79</v>
+      </c>
+      <c r="E473" t="n">
+        <v>1506.79</v>
+      </c>
+      <c r="F473" t="b">
+        <v>0</v>
+      </c>
+      <c r="G473" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>SI Table S8, Cu, 260 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>973.038</v>
+      </c>
+      <c r="D474" t="n">
+        <v>1041.44</v>
+      </c>
+      <c r="E474" t="n">
+        <v>1467.52</v>
+      </c>
+      <c r="F474" t="b">
+        <v>0</v>
+      </c>
+      <c r="G474" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>SI Table S8, Cu, 280 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>896.112</v>
+      </c>
+      <c r="D475" t="n">
+        <v>937.508</v>
+      </c>
+      <c r="E475" t="n">
+        <v>1764.01</v>
+      </c>
+      <c r="F475" t="b">
+        <v>1</v>
+      </c>
+      <c r="G475" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>SI Table S8, CuGa1.5, 220 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>1393.08</v>
+      </c>
+      <c r="D476" t="n">
+        <v>1572.17</v>
+      </c>
+      <c r="E476" t="n">
+        <v>1572.17</v>
+      </c>
+      <c r="F476" t="b">
+        <v>0</v>
+      </c>
+      <c r="G476" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>SI Table S8, CuGa1.5, 230 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>1211.17</v>
+      </c>
+      <c r="D477" t="n">
+        <v>1408.84</v>
+      </c>
+      <c r="E477" t="n">
+        <v>1408.84</v>
+      </c>
+      <c r="F477" t="b">
+        <v>0</v>
+      </c>
+      <c r="G477" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>SI Table S8, CuGa1.5, 240 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>1070.36</v>
+      </c>
+      <c r="D478" t="n">
+        <v>1256.05</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1302.54</v>
+      </c>
+      <c r="F478" t="b">
+        <v>0</v>
+      </c>
+      <c r="G478" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>SI Table S8, CuGa1.5, 260 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>945.699</v>
+      </c>
+      <c r="D479" t="n">
+        <v>983.467</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1297.26</v>
+      </c>
+      <c r="F479" t="b">
+        <v>0</v>
+      </c>
+      <c r="G479" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>SI Table S8, CuGa1.5, 280 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>894.259</v>
+      </c>
+      <c r="D480" t="n">
+        <v>945.146</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1588.41</v>
+      </c>
+      <c r="F480" t="b">
+        <v>1</v>
+      </c>
+      <c r="G480" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>SI Table S8, CuGa2.5, 230 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>1270.43</v>
+      </c>
+      <c r="D481" t="n">
+        <v>1543.6</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1543.6</v>
+      </c>
+      <c r="F481" t="b">
+        <v>0</v>
+      </c>
+      <c r="G481" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>SI Table S8, CuGa2.5, 260 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>971.5599999999999</v>
+      </c>
+      <c r="D482" t="n">
+        <v>1036.06</v>
+      </c>
+      <c r="E482" t="n">
+        <v>1424.32</v>
+      </c>
+      <c r="F482" t="b">
+        <v>0</v>
+      </c>
+      <c r="G482" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>SI Table S8, CuGa2.5, 280 °C, 20 bar</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>899.591</v>
+      </c>
+      <c r="D483" t="n">
+        <v>938.974</v>
+      </c>
+      <c r="E483" t="n">
+        <v>1697.26</v>
+      </c>
+      <c r="F483" t="b">
+        <v>1</v>
+      </c>
+      <c r="G483" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 2 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>SI Table S5, GaZr/90Cu, CO2:H2:N2=30:60:10</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>953.604</v>
+      </c>
+      <c r="D484" t="n">
+        <v>1007.73</v>
+      </c>
+      <c r="E484" t="n">
+        <v>1047.89</v>
+      </c>
+      <c r="F484" t="b">
+        <v>0</v>
+      </c>
+      <c r="G484" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 2 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>SI Table S5, ZnZr/90Cu, CO2:H2:N2=30:60:10</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>894.761</v>
+      </c>
+      <c r="D485" t="n">
+        <v>907.207</v>
+      </c>
+      <c r="E485" t="n">
+        <v>1081.84</v>
+      </c>
+      <c r="F485" t="b">
+        <v>1</v>
+      </c>
+      <c r="G485" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Figure 2a, GaZr/90Cu, 240 °C, 48000 mL/gcat./h</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>965.987</v>
+      </c>
+      <c r="D486" t="n">
+        <v>1016.94</v>
+      </c>
+      <c r="E486" t="n">
+        <v>1111.02</v>
+      </c>
+      <c r="F486" t="b">
+        <v>0</v>
+      </c>
+      <c r="G486" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Figure 2a/Table S3 text, ZnZr/90Cu, 240 °C, 48000 mL/gcat./h</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>900.235</v>
+      </c>
+      <c r="D487" t="n">
+        <v>911.504</v>
+      </c>
+      <c r="E487" t="n">
+        <v>1095.68</v>
+      </c>
+      <c r="F487" t="b">
+        <v>1</v>
+      </c>
+      <c r="G487" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 4 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>SI Table S5, GaZr/90Cu, CO2:H2:N2=19:76:5</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>1627.62</v>
+      </c>
+      <c r="D488" t="n">
+        <v>2581.52</v>
+      </c>
+      <c r="E488" t="n">
+        <v>2581.52</v>
+      </c>
+      <c r="F488" t="b">
+        <v>0</v>
+      </c>
+      <c r="G488" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 4 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>SI Table S5, ZnZr/90Cu, CO2:H2:N2=19:76:5</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>905.505</v>
+      </c>
+      <c r="D489" t="n">
+        <v>916</v>
+      </c>
+      <c r="E489" t="n">
+        <v>1105.72</v>
+      </c>
+      <c r="F489" t="b">
+        <v>1</v>
+      </c>
+      <c r="G489" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c05217 | 32 bar | H2/CO2 3 | 8 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Figure 1c, Cu@UiO-36AA-PSE, 260 °C</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>967.535</v>
+      </c>
+      <c r="D490" t="n">
+        <v>1011.7</v>
+      </c>
+      <c r="E490" t="n">
+        <v>1770.57</v>
+      </c>
+      <c r="F490" t="b">
+        <v>1</v>
+      </c>
+      <c r="G490" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c05217 | 32 bar | H2/CO2 3 | 8 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Figure 1c, Cu/ZrO2, 260 °C</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>1070.73</v>
+      </c>
+      <c r="D491" t="n">
+        <v>1284.73</v>
+      </c>
+      <c r="E491" t="n">
+        <v>2295.1</v>
+      </c>
+      <c r="F491" t="b">
+        <v>0</v>
+      </c>
+      <c r="G491" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06647 | 50 bar | H2/CO2 3 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>SI Table S2 ZnO</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>5441.03</v>
+      </c>
+      <c r="D492" t="n">
+        <v>5441.03</v>
+      </c>
+      <c r="E492" t="n">
+        <v>5441.03</v>
+      </c>
+      <c r="F492" t="b">
+        <v>0</v>
+      </c>
+      <c r="G492" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06647 | 50 bar | H2/CO2 3 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>SI Table S2 ZnSO4-derived residues</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>2438.95</v>
+      </c>
+      <c r="D493" t="n">
+        <v>2438.95</v>
+      </c>
+      <c r="E493" t="n">
+        <v>2438.95</v>
+      </c>
+      <c r="F493" t="b">
+        <v>0</v>
+      </c>
+      <c r="G493" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06647 | 50 bar | H2/CO2 3 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>SI Table S2 physical mixtures of ZnS + MoS2</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>1270.47</v>
+      </c>
+      <c r="D494" t="n">
+        <v>1279.05</v>
+      </c>
+      <c r="E494" t="n">
+        <v>1476.41</v>
+      </c>
+      <c r="F494" t="b">
+        <v>0</v>
+      </c>
+      <c r="G494" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06647 | 50 bar | H2/CO2 3 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>SI Table S2 impregnated Zn/MoS2</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>1022.98</v>
+      </c>
+      <c r="D495" t="n">
+        <v>1031.32</v>
+      </c>
+      <c r="E495" t="n">
+        <v>1062.02</v>
+      </c>
+      <c r="F495" t="b">
+        <v>1</v>
+      </c>
+      <c r="G495" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Figure 1b, In2O3-R, 220 °C</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>1792.58</v>
+      </c>
+      <c r="D496" t="n">
+        <v>1826.61</v>
+      </c>
+      <c r="E496" t="n">
+        <v>1826.61</v>
+      </c>
+      <c r="F496" t="b">
+        <v>0</v>
+      </c>
+      <c r="G496" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Figure 1b, In2O3-R, 240 °C</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>1172.95</v>
+      </c>
+      <c r="D497" t="n">
+        <v>1274.16</v>
+      </c>
+      <c r="E497" t="n">
+        <v>1274.16</v>
+      </c>
+      <c r="F497" t="b">
+        <v>0</v>
+      </c>
+      <c r="G497" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Figure 1b, In2O3-R, 260 °C</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>1046.68</v>
+      </c>
+      <c r="D498" t="n">
+        <v>1177.16</v>
+      </c>
+      <c r="E498" t="n">
+        <v>1177.16</v>
+      </c>
+      <c r="F498" t="b">
+        <v>0</v>
+      </c>
+      <c r="G498" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Figure 1b, In2O3-R, 280 °C</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>990.64</v>
+      </c>
+      <c r="D499" t="n">
+        <v>1093.6</v>
+      </c>
+      <c r="E499" t="n">
+        <v>1211.1</v>
+      </c>
+      <c r="F499" t="b">
+        <v>0</v>
+      </c>
+      <c r="G499" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Figure 1b, In2O3-R, 300 °C</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>941.306</v>
+      </c>
+      <c r="D500" t="n">
+        <v>989.277</v>
+      </c>
+      <c r="E500" t="n">
+        <v>1315.47</v>
+      </c>
+      <c r="F500" t="b">
+        <v>0</v>
+      </c>
+      <c r="G500" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/In2O3-R, 220 °C</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>1113.21</v>
+      </c>
+      <c r="D501" t="n">
+        <v>1144.29</v>
+      </c>
+      <c r="E501" t="n">
+        <v>1144.29</v>
+      </c>
+      <c r="F501" t="b">
+        <v>0</v>
+      </c>
+      <c r="G501" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/In2O3-R, 240 °C</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>1027.03</v>
+      </c>
+      <c r="D502" t="n">
+        <v>1071.84</v>
+      </c>
+      <c r="E502" t="n">
+        <v>1071.84</v>
+      </c>
+      <c r="F502" t="b">
+        <v>0</v>
+      </c>
+      <c r="G502" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/In2O3-R, 260 °C</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>962.126</v>
+      </c>
+      <c r="D503" t="n">
+        <v>1004.63</v>
+      </c>
+      <c r="E503" t="n">
+        <v>1018.54</v>
+      </c>
+      <c r="F503" t="b">
+        <v>0</v>
+      </c>
+      <c r="G503" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/In2O3-R, 280 °C</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>934.854</v>
+      </c>
+      <c r="D504" t="n">
+        <v>966.242</v>
+      </c>
+      <c r="E504" t="n">
+        <v>1058.91</v>
+      </c>
+      <c r="F504" t="b">
+        <v>0</v>
+      </c>
+      <c r="G504" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/In2O3-R, 300 °C</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>915.931</v>
+      </c>
+      <c r="D505" t="n">
+        <v>940.3440000000001</v>
+      </c>
+      <c r="E505" t="n">
+        <v>1154.61</v>
+      </c>
+      <c r="F505" t="b">
+        <v>1</v>
+      </c>
+      <c r="G505" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Figure 1b, CNT+In2O3-R, 240 °C</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>1056.33</v>
+      </c>
+      <c r="D506" t="n">
+        <v>1074.34</v>
+      </c>
+      <c r="E506" t="n">
+        <v>1074.34</v>
+      </c>
+      <c r="F506" t="b">
+        <v>0</v>
+      </c>
+      <c r="G506" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Figure 1b, CNT+In2O3-R, 260 °C</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>968.2809999999999</v>
+      </c>
+      <c r="D507" t="n">
+        <v>1011.55</v>
+      </c>
+      <c r="E507" t="n">
+        <v>1013.75</v>
+      </c>
+      <c r="F507" t="b">
+        <v>0</v>
+      </c>
+      <c r="G507" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Figure 1b, CNT+In2O3-R, 280 °C</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>935.529</v>
+      </c>
+      <c r="D508" t="n">
+        <v>964.133</v>
+      </c>
+      <c r="E508" t="n">
+        <v>1012.51</v>
+      </c>
+      <c r="F508" t="b">
+        <v>0</v>
+      </c>
+      <c r="G508" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Figure 1b, CNT+In2O3-R, 300 °C</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>915.1849999999999</v>
+      </c>
+      <c r="D509" t="n">
+        <v>936.336</v>
+      </c>
+      <c r="E509" t="n">
+        <v>1070.34</v>
+      </c>
+      <c r="F509" t="b">
+        <v>0</v>
+      </c>
+      <c r="G509" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/CNT+In2O3-R, 220 °C</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>1040.27</v>
+      </c>
+      <c r="D510" t="n">
+        <v>1054.33</v>
+      </c>
+      <c r="E510" t="n">
+        <v>1054.33</v>
+      </c>
+      <c r="F510" t="b">
+        <v>0</v>
+      </c>
+      <c r="G510" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/CNT+In2O3-R, 240 °C</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>954.949</v>
+      </c>
+      <c r="D511" t="n">
+        <v>977.563</v>
+      </c>
+      <c r="E511" t="n">
+        <v>1002.11</v>
+      </c>
+      <c r="F511" t="b">
+        <v>0</v>
+      </c>
+      <c r="G511" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/CNT+In2O3-R, 260 °C</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>925.333</v>
+      </c>
+      <c r="D512" t="n">
+        <v>940.98</v>
+      </c>
+      <c r="E512" t="n">
+        <v>999.884</v>
+      </c>
+      <c r="F512" t="b">
+        <v>0</v>
+      </c>
+      <c r="G512" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/CNT+In2O3-R, 280 °C</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>906.97</v>
+      </c>
+      <c r="D513" t="n">
+        <v>918.982</v>
+      </c>
+      <c r="E513" t="n">
+        <v>1040.76</v>
+      </c>
+      <c r="F513" t="b">
+        <v>0</v>
+      </c>
+      <c r="G513" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Figure 1b, Pd/CNT+In2O3-R, 300 °C</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>894.569</v>
+      </c>
+      <c r="D514" t="n">
+        <v>904.2809999999999</v>
+      </c>
+      <c r="E514" t="n">
+        <v>1161.41</v>
+      </c>
+      <c r="F514" t="b">
+        <v>1</v>
+      </c>
+      <c r="G514" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06780 | 30 bar | H2/CO2 4 | 40 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Figure 2a, CZA</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>871.0599999999999</v>
+      </c>
+      <c r="D515" t="n">
+        <v>873.702</v>
+      </c>
+      <c r="E515" t="n">
+        <v>1479.77</v>
+      </c>
+      <c r="F515" t="b">
+        <v>0</v>
+      </c>
+      <c r="G515" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06780 | 30 bar | H2/CO2 4 | 40 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Figure 2a, CZA-2Zr</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>862.77</v>
+      </c>
+      <c r="D516" t="n">
+        <v>864.647</v>
+      </c>
+      <c r="E516" t="n">
+        <v>1437.89</v>
+      </c>
+      <c r="F516" t="b">
+        <v>1</v>
+      </c>
+      <c r="G516" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06780 | 30 bar | H2/CO2 4 | 40 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Figure 2a, CZA-8Zr</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>875.795</v>
+      </c>
+      <c r="D517" t="n">
+        <v>878.987</v>
+      </c>
+      <c r="E517" t="n">
+        <v>1330.99</v>
+      </c>
+      <c r="F517" t="b">
+        <v>0</v>
+      </c>
+      <c r="G517" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06780 | 30 bar | H2/CO2 4 | 40 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Figure 2b, CA</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>954.777</v>
+      </c>
+      <c r="D518" t="n">
+        <v>978.384</v>
+      </c>
+      <c r="E518" t="n">
+        <v>2107.02</v>
+      </c>
+      <c r="F518" t="b">
+        <v>0</v>
+      </c>
+      <c r="G518" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06780 | 30 bar | H2/CO2 4 | 40 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Figure 2b, CA-2Zr</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>979.155</v>
+      </c>
+      <c r="D519" t="n">
+        <v>1016.97</v>
+      </c>
+      <c r="E519" t="n">
+        <v>1775.58</v>
+      </c>
+      <c r="F519" t="b">
+        <v>0</v>
+      </c>
+      <c r="G519" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.6c05638 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Figure 1a / Figure 10a, CZA, ICCU, 300 °C, 3 MPa</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>844.105</v>
+      </c>
+      <c r="D520" t="n">
+        <v>922.279</v>
+      </c>
+      <c r="E520" t="n">
+        <v>2549.05</v>
+      </c>
+      <c r="F520" t="b">
+        <v>1</v>
+      </c>
+      <c r="G520" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.6c05638 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Figure 1a / Figure 10b, CZC-OA, ICCU, 300 °C, 3 MPa</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>837.763</v>
+      </c>
+      <c r="D521" t="n">
+        <v>918.461</v>
+      </c>
+      <c r="E521" t="n">
+        <v>1684.04</v>
+      </c>
+      <c r="F521" t="b">
+        <v>1</v>
+      </c>
+      <c r="G521" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.6c05638 | 30 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Figure 10b, CZC-OA, CO2+H2 co-feed, 300 °C, 3 MPa</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>865.0599999999999</v>
+      </c>
+      <c r="D522" t="n">
+        <v>926.548</v>
+      </c>
+      <c r="E522" t="n">
+        <v>2298.2</v>
+      </c>
+      <c r="F522" t="b">
+        <v>1</v>
+      </c>
+      <c r="G522" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 6</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>913.497</v>
+      </c>
+      <c r="D523" t="n">
+        <v>928.864</v>
+      </c>
+      <c r="E523" t="n">
+        <v>1055.02</v>
+      </c>
+      <c r="F523" t="b">
+        <v>0</v>
+      </c>
+      <c r="G523" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 7</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>901.753</v>
+      </c>
+      <c r="D524" t="n">
+        <v>912.3150000000001</v>
+      </c>
+      <c r="E524" t="n">
+        <v>1048.88</v>
+      </c>
+      <c r="F524" t="b">
+        <v>0</v>
+      </c>
+      <c r="G524" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 8</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>923.138</v>
+      </c>
+      <c r="D525" t="n">
+        <v>943.259</v>
+      </c>
+      <c r="E525" t="n">
+        <v>1083.32</v>
+      </c>
+      <c r="F525" t="b">
+        <v>0</v>
+      </c>
+      <c r="G525" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 9</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>887.508</v>
+      </c>
+      <c r="D526" t="n">
+        <v>893.403</v>
+      </c>
+      <c r="E526" t="n">
+        <v>1163.65</v>
+      </c>
+      <c r="F526" t="b">
+        <v>0</v>
+      </c>
+      <c r="G526" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 10</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>1324.57</v>
+      </c>
+      <c r="D527" t="n">
+        <v>3549.64</v>
+      </c>
+      <c r="E527" t="n">
+        <v>15390.6</v>
+      </c>
+      <c r="F527" t="b">
+        <v>0</v>
+      </c>
+      <c r="G527" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 11</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>870.683</v>
+      </c>
+      <c r="D528" t="n">
+        <v>873.495</v>
+      </c>
+      <c r="E528" t="n">
+        <v>1167.92</v>
+      </c>
+      <c r="F528" t="b">
+        <v>1</v>
+      </c>
+      <c r="G528" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 12</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>867.682</v>
+      </c>
+      <c r="D529" t="n">
+        <v>873.03</v>
+      </c>
+      <c r="E529" t="n">
+        <v>1148.42</v>
+      </c>
+      <c r="F529" t="b">
+        <v>1</v>
+      </c>
+      <c r="G529" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 50 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Text, LDH-NiInCAl, 260 °C, 5 MPa</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>868.849</v>
+      </c>
+      <c r="D530" t="n">
+        <v>870.777</v>
+      </c>
+      <c r="E530" t="n">
+        <v>1110.42</v>
+      </c>
+      <c r="F530" t="b">
+        <v>1</v>
+      </c>
+      <c r="G530" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-025-65929-z | 50 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>SI Table S7 row 3</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>902.822</v>
+      </c>
+      <c r="D531" t="n">
+        <v>915.343</v>
+      </c>
+      <c r="E531" t="n">
+        <v>1112.3</v>
+      </c>
+      <c r="F531" t="b">
+        <v>0</v>
+      </c>
+      <c r="G531" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-72876-w | 20 bar | H2/CO2 3 | 450 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Fig. 4a/text, In1.9Sn0.1O3.05 initial TOS</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>4923.43</v>
+      </c>
+      <c r="D532" t="n">
+        <v>6857.19</v>
+      </c>
+      <c r="E532" t="n">
+        <v>6857.19</v>
+      </c>
+      <c r="F532" t="b">
+        <v>0</v>
+      </c>
+      <c r="G532" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-72876-w | 20 bar | H2/CO2 3 | 450 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Fig. 4a/text, In1.9Zr0.1O3.05 initial TOS</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>1399.3</v>
+      </c>
+      <c r="D533" t="n">
+        <v>1985.94</v>
+      </c>
+      <c r="E533" t="n">
+        <v>1985.94</v>
+      </c>
+      <c r="F533" t="b">
+        <v>1</v>
+      </c>
+      <c r="G533" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-72876-w | 20 bar | H2/CO2 3 | 450 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Fig. 4a/text, nano-In2O3 stable initial period</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>2624.33</v>
+      </c>
+      <c r="D534" t="n">
+        <v>4007.96</v>
+      </c>
+      <c r="E534" t="n">
+        <v>4007.96</v>
+      </c>
+      <c r="F534" t="b">
+        <v>0</v>
+      </c>
+      <c r="G534" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-72876-w | 20 bar | H2/CO2 3 | 450 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Fig. 6a state 1, In1.9Zr0.1O3.05 standard after 4 h</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>1399.22</v>
+      </c>
+      <c r="D535" t="n">
+        <v>1961.83</v>
+      </c>
+      <c r="E535" t="n">
+        <v>1961.83</v>
+      </c>
+      <c r="F535" t="b">
+        <v>1</v>
+      </c>
+      <c r="G535" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Text p2, PtMo6O24@NU1K at 100 °C</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>1243.16</v>
+      </c>
+      <c r="D536" t="n">
+        <v>1254.03</v>
+      </c>
+      <c r="E536" t="n">
+        <v>1392.38</v>
+      </c>
+      <c r="F536" t="b">
+        <v>0</v>
+      </c>
+      <c r="G536" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Text p2/p8, PtMo6O24@NU1K at 200 °C</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>885.745</v>
+      </c>
+      <c r="D537" t="n">
+        <v>886.769</v>
+      </c>
+      <c r="E537" t="n">
+        <v>1114.41</v>
+      </c>
+      <c r="F537" t="b">
+        <v>0</v>
+      </c>
+      <c r="G537" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, PtMo6O24@NU1K at 180 °C</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>895.2910000000001</v>
+      </c>
+      <c r="D538" t="n">
+        <v>895.995</v>
+      </c>
+      <c r="E538" t="n">
+        <v>1026.23</v>
+      </c>
+      <c r="F538" t="b">
+        <v>0</v>
+      </c>
+      <c r="G538" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Fig. 1e stability, PtMo6O24@NU1K at 180 °C over 3,600 h</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>891.825</v>
+      </c>
+      <c r="D539" t="n">
+        <v>892.442</v>
+      </c>
+      <c r="E539" t="n">
+        <v>999.9</v>
+      </c>
+      <c r="F539" t="b">
+        <v>0</v>
+      </c>
+      <c r="G539" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, PtMo6O24/ZrO2 at 180 °C</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>1391.77</v>
+      </c>
+      <c r="D540" t="n">
+        <v>1405.07</v>
+      </c>
+      <c r="E540" t="n">
+        <v>14251.8</v>
+      </c>
+      <c r="F540" t="b">
+        <v>0</v>
+      </c>
+      <c r="G540" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, Pt@NU1K at 180 °C</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>2315.32</v>
+      </c>
+      <c r="D541" t="n">
+        <v>12419.7</v>
+      </c>
+      <c r="E541" t="n">
+        <v>12419.7</v>
+      </c>
+      <c r="F541" t="b">
+        <v>0</v>
+      </c>
+      <c r="G541" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, PtV9O28@NU1K at 180 °C</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>1213.76</v>
+      </c>
+      <c r="D542" t="n">
+        <v>1266.46</v>
+      </c>
+      <c r="E542" t="n">
+        <v>2415.33</v>
+      </c>
+      <c r="F542" t="b">
+        <v>0</v>
+      </c>
+      <c r="G542" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, PtW6O24@NU1K at 180 °C</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>1177.52</v>
+      </c>
+      <c r="D543" t="n">
+        <v>1224.6</v>
+      </c>
+      <c r="E543" t="n">
+        <v>1959.45</v>
+      </c>
+      <c r="F543" t="b">
+        <v>0</v>
+      </c>
+      <c r="G543" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, PtMo6O24 SC at 180 °C</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>1055.92</v>
+      </c>
+      <c r="D544" t="n">
+        <v>1071.81</v>
+      </c>
+      <c r="E544" t="n">
+        <v>1441.32</v>
+      </c>
+      <c r="F544" t="b">
+        <v>0</v>
+      </c>
+      <c r="G544" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, PtMo6O24@NU901 at 180 °C</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>939.362</v>
+      </c>
+      <c r="D545" t="n">
+        <v>941.548</v>
+      </c>
+      <c r="E545" t="n">
+        <v>1277.89</v>
+      </c>
+      <c r="F545" t="b">
+        <v>0</v>
+      </c>
+      <c r="G545" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, PtMo6O24@NU1008 at 180 °C</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>914.342</v>
+      </c>
+      <c r="D546" t="n">
+        <v>915.569</v>
+      </c>
+      <c r="E546" t="n">
+        <v>1168.17</v>
+      </c>
+      <c r="F546" t="b">
+        <v>0</v>
+      </c>
+      <c r="G546" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Fig. 1d/text, PtMo6O24@Hf-NU1K at 180 °C</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>895.225</v>
+      </c>
+      <c r="D547" t="n">
+        <v>895.927</v>
+      </c>
+      <c r="E547" t="n">
+        <v>1024.1</v>
+      </c>
+      <c r="F547" t="b">
+        <v>0</v>
+      </c>
+      <c r="G547" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Text p2, ZnMo6O24@NU1K at 200 °C</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>1691.37</v>
+      </c>
+      <c r="D548" t="n">
+        <v>3217.37</v>
+      </c>
+      <c r="E548" t="n">
+        <v>5869.1</v>
+      </c>
+      <c r="F548" t="b">
+        <v>0</v>
+      </c>
+      <c r="G548" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Text p2, AlMo6O24@NU1K at 200 °C</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>1523.62</v>
+      </c>
+      <c r="D549" t="n">
+        <v>2681.89</v>
+      </c>
+      <c r="E549" t="n">
+        <v>2681.89</v>
+      </c>
+      <c r="F549" t="b">
+        <v>0</v>
+      </c>
+      <c r="G549" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@NU1K, 160°C</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>921.2670000000001</v>
+      </c>
+      <c r="D550" t="n">
+        <v>922.324</v>
+      </c>
+      <c r="E550" t="n">
+        <v>1052.63</v>
+      </c>
+      <c r="F550" t="b">
+        <v>0</v>
+      </c>
+      <c r="G550" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@NU1K, 140°C</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>961.7859999999999</v>
+      </c>
+      <c r="D551" t="n">
+        <v>963.436</v>
+      </c>
+      <c r="E551" t="n">
+        <v>1073.8</v>
+      </c>
+      <c r="F551" t="b">
+        <v>0</v>
+      </c>
+      <c r="G551" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@NU1K, 120°C</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>1042.26</v>
+      </c>
+      <c r="D552" t="n">
+        <v>1045.58</v>
+      </c>
+      <c r="E552" t="n">
+        <v>1153.71</v>
+      </c>
+      <c r="F552" t="b">
+        <v>0</v>
+      </c>
+      <c r="G552" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24/ZrO2, 200°C</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>1381.27</v>
+      </c>
+      <c r="D553" t="n">
+        <v>1395.6</v>
+      </c>
+      <c r="E553" t="n">
+        <v>17148.3</v>
+      </c>
+      <c r="F553" t="b">
+        <v>0</v>
+      </c>
+      <c r="G553" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24/ZrO2, 160°C</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>1610.03</v>
+      </c>
+      <c r="D554" t="n">
+        <v>1632.83</v>
+      </c>
+      <c r="E554" t="n">
+        <v>17699.6</v>
+      </c>
+      <c r="F554" t="b">
+        <v>0</v>
+      </c>
+      <c r="G554" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>SI Table S3, Pt@NU1K, 200°C</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>2156.55</v>
+      </c>
+      <c r="D555" t="n">
+        <v>11981.6</v>
+      </c>
+      <c r="E555" t="n">
+        <v>11981.6</v>
+      </c>
+      <c r="F555" t="b">
+        <v>0</v>
+      </c>
+      <c r="G555" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>SI Table S3, Pt@NU1K, 160°C</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>3326.09</v>
+      </c>
+      <c r="D556" t="n">
+        <v>18370.4</v>
+      </c>
+      <c r="E556" t="n">
+        <v>18370.4</v>
+      </c>
+      <c r="F556" t="b">
+        <v>0</v>
+      </c>
+      <c r="G556" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtW6O24@NU1K, 200°C</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>1053.41</v>
+      </c>
+      <c r="D557" t="n">
+        <v>1074.25</v>
+      </c>
+      <c r="E557" t="n">
+        <v>1690.18</v>
+      </c>
+      <c r="F557" t="b">
+        <v>0</v>
+      </c>
+      <c r="G557" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtW6O24@NU1K, 160°C</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>1291.27</v>
+      </c>
+      <c r="D558" t="n">
+        <v>1351.57</v>
+      </c>
+      <c r="E558" t="n">
+        <v>2502.84</v>
+      </c>
+      <c r="F558" t="b">
+        <v>0</v>
+      </c>
+      <c r="G558" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtV9O28@NU1K, 200°C</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>1119.69</v>
+      </c>
+      <c r="D559" t="n">
+        <v>1155.78</v>
+      </c>
+      <c r="E559" t="n">
+        <v>2208.86</v>
+      </c>
+      <c r="F559" t="b">
+        <v>0</v>
+      </c>
+      <c r="G559" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtV9O28@NU1K, 160°C</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>1258.83</v>
+      </c>
+      <c r="D560" t="n">
+        <v>1304.02</v>
+      </c>
+      <c r="E560" t="n">
+        <v>2550.39</v>
+      </c>
+      <c r="F560" t="b">
+        <v>0</v>
+      </c>
+      <c r="G560" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24 SC, 200°C</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>990.877</v>
+      </c>
+      <c r="D561" t="n">
+        <v>999.325</v>
+      </c>
+      <c r="E561" t="n">
+        <v>1524.27</v>
+      </c>
+      <c r="F561" t="b">
+        <v>0</v>
+      </c>
+      <c r="G561" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24 SC, 160°C</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>1214.3</v>
+      </c>
+      <c r="D562" t="n">
+        <v>1259.58</v>
+      </c>
+      <c r="E562" t="n">
+        <v>1766.11</v>
+      </c>
+      <c r="F562" t="b">
+        <v>0</v>
+      </c>
+      <c r="G562" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@NU901, 200°C</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>902.4829999999999</v>
+      </c>
+      <c r="D563" t="n">
+        <v>903.7859999999999</v>
+      </c>
+      <c r="E563" t="n">
+        <v>1090.24</v>
+      </c>
+      <c r="F563" t="b">
+        <v>0</v>
+      </c>
+      <c r="G563" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@NU901, 160°C</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>992.745</v>
+      </c>
+      <c r="D564" t="n">
+        <v>996.08</v>
+      </c>
+      <c r="E564" t="n">
+        <v>1619.15</v>
+      </c>
+      <c r="F564" t="b">
+        <v>0</v>
+      </c>
+      <c r="G564" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@NU1008, 200°C</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>891.692</v>
+      </c>
+      <c r="D565" t="n">
+        <v>892.586</v>
+      </c>
+      <c r="E565" t="n">
+        <v>1045.85</v>
+      </c>
+      <c r="F565" t="b">
+        <v>0</v>
+      </c>
+      <c r="G565" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@NU1008, 160°C</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>978.151</v>
+      </c>
+      <c r="D566" t="n">
+        <v>980.963</v>
+      </c>
+      <c r="E566" t="n">
+        <v>1485.04</v>
+      </c>
+      <c r="F566" t="b">
+        <v>0</v>
+      </c>
+      <c r="G566" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@Hf-NU1K, 200°C</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>884.409</v>
+      </c>
+      <c r="D567" t="n">
+        <v>885.265</v>
+      </c>
+      <c r="E567" t="n">
+        <v>1060.45</v>
+      </c>
+      <c r="F567" t="b">
+        <v>1</v>
+      </c>
+      <c r="G567" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>SI Table S3, PtMo6O24@Hf-NU1K, 160°C</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>921.561</v>
+      </c>
+      <c r="D568" t="n">
+        <v>922.619</v>
+      </c>
+      <c r="E568" t="n">
+        <v>1078.68</v>
+      </c>
+      <c r="F568" t="b">
+        <v>0</v>
+      </c>
+      <c r="G568" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Fig. 1b,c: 1InHfOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>1065.1</v>
+      </c>
+      <c r="D569" t="n">
+        <v>1387.01</v>
+      </c>
+      <c r="E569" t="n">
+        <v>2246.91</v>
+      </c>
+      <c r="F569" t="b">
+        <v>0</v>
+      </c>
+      <c r="G569" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Fig. 1b,c: 2InHfOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>979.877</v>
+      </c>
+      <c r="D570" t="n">
+        <v>1061.57</v>
+      </c>
+      <c r="E570" t="n">
+        <v>1339.7</v>
+      </c>
+      <c r="F570" t="b">
+        <v>0</v>
+      </c>
+      <c r="G570" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Fig. 1b,c: 5InHfOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>960.338</v>
+      </c>
+      <c r="D571" t="n">
+        <v>1018.13</v>
+      </c>
+      <c r="E571" t="n">
+        <v>1057.04</v>
+      </c>
+      <c r="F571" t="b">
+        <v>1</v>
+      </c>
+      <c r="G571" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Fig. 1b,c: 10InHfOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>940.421</v>
+      </c>
+      <c r="D572" t="n">
+        <v>976.165</v>
+      </c>
+      <c r="E572" t="n">
+        <v>1133.81</v>
+      </c>
+      <c r="F572" t="b">
+        <v>1</v>
+      </c>
+      <c r="G572" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Fig. 1b: 3InHfOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>959.098</v>
+      </c>
+      <c r="D573" t="n">
+        <v>1012.06</v>
+      </c>
+      <c r="E573" t="n">
+        <v>1334.87</v>
+      </c>
+      <c r="F573" t="b">
+        <v>1</v>
+      </c>
+      <c r="G573" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Fig. 1b: 7InHfOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>933.628</v>
+      </c>
+      <c r="D574" t="n">
+        <v>963.746</v>
+      </c>
+      <c r="E574" t="n">
+        <v>1124.77</v>
+      </c>
+      <c r="F574" t="b">
+        <v>1</v>
+      </c>
+      <c r="G574" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Fig. 1b,c: 1InZrOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>1128.16</v>
+      </c>
+      <c r="D575" t="n">
+        <v>2127.17</v>
+      </c>
+      <c r="E575" t="n">
+        <v>2621.27</v>
+      </c>
+      <c r="F575" t="b">
+        <v>0</v>
+      </c>
+      <c r="G575" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Fig. 1b,c: 2InZrOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>1053.42</v>
+      </c>
+      <c r="D576" t="n">
+        <v>1341.44</v>
+      </c>
+      <c r="E576" t="n">
+        <v>1729.3</v>
+      </c>
+      <c r="F576" t="b">
+        <v>0</v>
+      </c>
+      <c r="G576" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Fig. 1b,c: 5InZrOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>960.216</v>
+      </c>
+      <c r="D577" t="n">
+        <v>1015.53</v>
+      </c>
+      <c r="E577" t="n">
+        <v>1244.23</v>
+      </c>
+      <c r="F577" t="b">
+        <v>1</v>
+      </c>
+      <c r="G577" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Fig. 1b,c: 10InZrOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>944.638</v>
+      </c>
+      <c r="D578" t="n">
+        <v>983.116</v>
+      </c>
+      <c r="E578" t="n">
+        <v>1269.95</v>
+      </c>
+      <c r="F578" t="b">
+        <v>1</v>
+      </c>
+      <c r="G578" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Fig. 1b: 3InZrOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>994.579</v>
+      </c>
+      <c r="D579" t="n">
+        <v>1097.28</v>
+      </c>
+      <c r="E579" t="n">
+        <v>1632.99</v>
+      </c>
+      <c r="F579" t="b">
+        <v>0</v>
+      </c>
+      <c r="G579" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Fig. 1b: 7InZrOx, 553 K</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>966.458</v>
+      </c>
+      <c r="D580" t="n">
+        <v>1029.91</v>
+      </c>
+      <c r="E580" t="n">
+        <v>1230.42</v>
+      </c>
+      <c r="F580" t="b">
+        <v>0</v>
+      </c>
+      <c r="G580" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Fig. 1b: In2O3/HfO2(FSP),WI, 553 K</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>960.569</v>
+      </c>
+      <c r="D581" t="n">
+        <v>1013.56</v>
+      </c>
+      <c r="E581" t="n">
+        <v>1495.73</v>
+      </c>
+      <c r="F581" t="b">
+        <v>1</v>
+      </c>
+      <c r="G581" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Fig. 1b: InHfOx,CP, 553 K</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>1382.03</v>
+      </c>
+      <c r="D582" t="n">
+        <v>22911.5</v>
+      </c>
+      <c r="E582" t="n">
+        <v>22911.5</v>
+      </c>
+      <c r="F582" t="b">
+        <v>0</v>
+      </c>
+      <c r="G582" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Fig. 1b: In2O3/HfO2(P),WI, 553 K</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>1613.76</v>
+      </c>
+      <c r="D583" t="n">
+        <v>71324.3</v>
+      </c>
+      <c r="E583" t="n">
+        <v>71324.3</v>
+      </c>
+      <c r="F583" t="b">
+        <v>0</v>
+      </c>
+      <c r="G583" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Table S3 entry 1, 220 °C</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>2046.34</v>
+      </c>
+      <c r="D584" t="n">
+        <v>2046.34</v>
+      </c>
+      <c r="E584" t="n">
+        <v>2046.34</v>
+      </c>
+      <c r="F584" t="b">
+        <v>0</v>
+      </c>
+      <c r="G584" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Table S3 entry 1, 240 °C</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>1408.22</v>
+      </c>
+      <c r="D585" t="n">
+        <v>1408.22</v>
+      </c>
+      <c r="E585" t="n">
+        <v>1408.22</v>
+      </c>
+      <c r="F585" t="b">
+        <v>0</v>
+      </c>
+      <c r="G585" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Table S3 entry 1, 260 °C</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>1061.72</v>
+      </c>
+      <c r="D586" t="n">
+        <v>1061.72</v>
+      </c>
+      <c r="E586" t="n">
+        <v>1061.72</v>
+      </c>
+      <c r="F586" t="b">
+        <v>0</v>
+      </c>
+      <c r="G586" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Table S3 entry 1, 280 °C</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>970.644</v>
+      </c>
+      <c r="D587" t="n">
+        <v>1037.68</v>
+      </c>
+      <c r="E587" t="n">
+        <v>1162.67</v>
+      </c>
+      <c r="F587" t="b">
+        <v>0</v>
+      </c>
+      <c r="G587" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Table S3 entry 1, 300 °C</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>922.526</v>
+      </c>
+      <c r="D588" t="n">
+        <v>949.122</v>
+      </c>
+      <c r="E588" t="n">
+        <v>1124.88</v>
+      </c>
+      <c r="F588" t="b">
+        <v>1</v>
+      </c>
+      <c r="G588" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Table S3 entry 1, 320 °C</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>902.63</v>
+      </c>
+      <c r="D589" t="n">
+        <v>922.614</v>
+      </c>
+      <c r="E589" t="n">
+        <v>1207.06</v>
+      </c>
+      <c r="F589" t="b">
+        <v>1</v>
+      </c>
+      <c r="G589" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Table S3 entry 2, 220 °C</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>3756.48</v>
+      </c>
+      <c r="D590" t="n">
+        <v>3756.48</v>
+      </c>
+      <c r="E590" t="n">
+        <v>3756.48</v>
+      </c>
+      <c r="F590" t="b">
+        <v>0</v>
+      </c>
+      <c r="G590" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Table S3 entry 2, 240 °C</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>2334.69</v>
+      </c>
+      <c r="D591" t="n">
+        <v>2334.69</v>
+      </c>
+      <c r="E591" t="n">
+        <v>2334.69</v>
+      </c>
+      <c r="F591" t="b">
+        <v>0</v>
+      </c>
+      <c r="G591" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Table S3 entry 2, 260 °C</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>1609.68</v>
+      </c>
+      <c r="D592" t="n">
+        <v>1609.68</v>
+      </c>
+      <c r="E592" t="n">
+        <v>1609.68</v>
+      </c>
+      <c r="F592" t="b">
+        <v>0</v>
+      </c>
+      <c r="G592" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Table S3 entry 2, 280 °C</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>1129.23</v>
+      </c>
+      <c r="D593" t="n">
+        <v>1465.46</v>
+      </c>
+      <c r="E593" t="n">
+        <v>1465.46</v>
+      </c>
+      <c r="F593" t="b">
+        <v>0</v>
+      </c>
+      <c r="G593" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Table S3 entry 2, 300 °C</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>1050.71</v>
+      </c>
+      <c r="D594" t="n">
+        <v>1354.01</v>
+      </c>
+      <c r="E594" t="n">
+        <v>1354.01</v>
+      </c>
+      <c r="F594" t="b">
+        <v>0</v>
+      </c>
+      <c r="G594" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Table S3 entry 2, 320 °C</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>1031.95</v>
+      </c>
+      <c r="D595" t="n">
+        <v>1341.69</v>
+      </c>
+      <c r="E595" t="n">
+        <v>1408.52</v>
+      </c>
+      <c r="F595" t="b">
+        <v>0</v>
+      </c>
+      <c r="G595" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Table S3 entry 3, 220 °C</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>2047.35</v>
+      </c>
+      <c r="D596" t="n">
+        <v>2047.35</v>
+      </c>
+      <c r="E596" t="n">
+        <v>2047.35</v>
+      </c>
+      <c r="F596" t="b">
+        <v>0</v>
+      </c>
+      <c r="G596" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Table S3 entry 3, 240 °C</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>1461.43</v>
+      </c>
+      <c r="D597" t="n">
+        <v>1461.43</v>
+      </c>
+      <c r="E597" t="n">
+        <v>1461.43</v>
+      </c>
+      <c r="F597" t="b">
+        <v>0</v>
+      </c>
+      <c r="G597" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Table S3 entry 3, 260 °C</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>1037.1</v>
+      </c>
+      <c r="D598" t="n">
+        <v>1190.47</v>
+      </c>
+      <c r="E598" t="n">
+        <v>1259.85</v>
+      </c>
+      <c r="F598" t="b">
+        <v>0</v>
+      </c>
+      <c r="G598" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Table S3 entry 3, 280 °C</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>963.799</v>
+      </c>
+      <c r="D599" t="n">
+        <v>1015.47</v>
+      </c>
+      <c r="E599" t="n">
+        <v>1175.2</v>
+      </c>
+      <c r="F599" t="b">
+        <v>0</v>
+      </c>
+      <c r="G599" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Table S3 entry 3, 300 °C</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>922.3339999999999</v>
+      </c>
+      <c r="D600" t="n">
+        <v>943.276</v>
+      </c>
+      <c r="E600" t="n">
+        <v>1122.72</v>
+      </c>
+      <c r="F600" t="b">
+        <v>1</v>
+      </c>
+      <c r="G600" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Table S3 entry 3, 320 °C</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>908.8</v>
+      </c>
+      <c r="D601" t="n">
+        <v>933.893</v>
+      </c>
+      <c r="E601" t="n">
+        <v>1215.72</v>
+      </c>
+      <c r="F601" t="b">
+        <v>1</v>
+      </c>
+      <c r="G601" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Table S3 entry 4, 220 °C</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>2808.16</v>
+      </c>
+      <c r="D602" t="n">
+        <v>2808.16</v>
+      </c>
+      <c r="E602" t="n">
+        <v>2808.16</v>
+      </c>
+      <c r="F602" t="b">
+        <v>0</v>
+      </c>
+      <c r="G602" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Table S3 entry 4, 240 °C</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>1852.57</v>
+      </c>
+      <c r="D603" t="n">
+        <v>1852.57</v>
+      </c>
+      <c r="E603" t="n">
+        <v>1852.57</v>
+      </c>
+      <c r="F603" t="b">
+        <v>0</v>
+      </c>
+      <c r="G603" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Table S3 entry 4, 260 °C</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>1363.24</v>
+      </c>
+      <c r="D604" t="n">
+        <v>1363.24</v>
+      </c>
+      <c r="E604" t="n">
+        <v>1363.24</v>
+      </c>
+      <c r="F604" t="b">
+        <v>0</v>
+      </c>
+      <c r="G604" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Table S3 entry 4, 280 °C</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>1048.93</v>
+      </c>
+      <c r="D605" t="n">
+        <v>1288.76</v>
+      </c>
+      <c r="E605" t="n">
+        <v>1288.76</v>
+      </c>
+      <c r="F605" t="b">
+        <v>0</v>
+      </c>
+      <c r="G605" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Table S3 entry 4, 300 °C</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>960.183</v>
+      </c>
+      <c r="D606" t="n">
+        <v>1026.18</v>
+      </c>
+      <c r="E606" t="n">
+        <v>1185.17</v>
+      </c>
+      <c r="F606" t="b">
+        <v>0</v>
+      </c>
+      <c r="G606" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Table S3 entry 4, 320 °C</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>925.147</v>
+      </c>
+      <c r="D607" t="n">
+        <v>954.497</v>
+      </c>
+      <c r="E607" t="n">
+        <v>1154.53</v>
+      </c>
+      <c r="F607" t="b">
+        <v>0</v>
+      </c>
+      <c r="G607" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Table S3 entry 5, 220 °C</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>2804.09</v>
+      </c>
+      <c r="D608" t="n">
+        <v>2804.09</v>
+      </c>
+      <c r="E608" t="n">
+        <v>2804.09</v>
+      </c>
+      <c r="F608" t="b">
+        <v>0</v>
+      </c>
+      <c r="G608" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Table S3 entry 5, 240 °C</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>1713.94</v>
+      </c>
+      <c r="D609" t="n">
+        <v>1713.94</v>
+      </c>
+      <c r="E609" t="n">
+        <v>1713.94</v>
+      </c>
+      <c r="F609" t="b">
+        <v>0</v>
+      </c>
+      <c r="G609" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Table S3 entry 5, 260 °C</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>1263.34</v>
+      </c>
+      <c r="D610" t="n">
+        <v>1263.34</v>
+      </c>
+      <c r="E610" t="n">
+        <v>1263.34</v>
+      </c>
+      <c r="F610" t="b">
+        <v>0</v>
+      </c>
+      <c r="G610" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Table S3 entry 5, 280 °C</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>1010.8</v>
+      </c>
+      <c r="D611" t="n">
+        <v>1145.87</v>
+      </c>
+      <c r="E611" t="n">
+        <v>1243.83</v>
+      </c>
+      <c r="F611" t="b">
+        <v>0</v>
+      </c>
+      <c r="G611" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Table S3 entry 5, 300 °C</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>948.787</v>
+      </c>
+      <c r="D612" t="n">
+        <v>998.9400000000001</v>
+      </c>
+      <c r="E612" t="n">
+        <v>1166.49</v>
+      </c>
+      <c r="F612" t="b">
+        <v>0</v>
+      </c>
+      <c r="G612" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Table S3 entry 5, 320 °C</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>922.323</v>
+      </c>
+      <c r="D613" t="n">
+        <v>948.943</v>
+      </c>
+      <c r="E613" t="n">
+        <v>1169.31</v>
+      </c>
+      <c r="F613" t="b">
+        <v>1</v>
+      </c>
+      <c r="G613" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Table S3 entry 6, 220 °C</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>3740.11</v>
+      </c>
+      <c r="D614" t="n">
+        <v>3740.11</v>
+      </c>
+      <c r="E614" t="n">
+        <v>3740.11</v>
+      </c>
+      <c r="F614" t="b">
+        <v>0</v>
+      </c>
+      <c r="G614" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Table S3 entry 6, 240 °C</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>2329.97</v>
+      </c>
+      <c r="D615" t="n">
+        <v>2329.97</v>
+      </c>
+      <c r="E615" t="n">
+        <v>2329.97</v>
+      </c>
+      <c r="F615" t="b">
+        <v>0</v>
+      </c>
+      <c r="G615" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Table S3 entry 6, 260 °C</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>1528.15</v>
+      </c>
+      <c r="D616" t="n">
+        <v>1528.15</v>
+      </c>
+      <c r="E616" t="n">
+        <v>1528.15</v>
+      </c>
+      <c r="F616" t="b">
+        <v>0</v>
+      </c>
+      <c r="G616" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Table S3 entry 6, 280 °C</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>1215.82</v>
+      </c>
+      <c r="D617" t="n">
+        <v>1215.82</v>
+      </c>
+      <c r="E617" t="n">
+        <v>1215.82</v>
+      </c>
+      <c r="F617" t="b">
+        <v>0</v>
+      </c>
+      <c r="G617" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Table S3 entry 6, 300 °C</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>992.261</v>
+      </c>
+      <c r="D618" t="n">
+        <v>1118.01</v>
+      </c>
+      <c r="E618" t="n">
+        <v>1324.02</v>
+      </c>
+      <c r="F618" t="b">
+        <v>0</v>
+      </c>
+      <c r="G618" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Table S3 entry 6, 320 °C</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>960.26</v>
+      </c>
+      <c r="D619" t="n">
+        <v>1040.99</v>
+      </c>
+      <c r="E619" t="n">
+        <v>1283.29</v>
+      </c>
+      <c r="F619" t="b">
+        <v>0</v>
+      </c>
+      <c r="G619" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Table S3 entry 7, 220 °C</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>5034.9</v>
+      </c>
+      <c r="D620" t="n">
+        <v>330997</v>
+      </c>
+      <c r="E620" t="n">
+        <v>330997</v>
+      </c>
+      <c r="F620" t="b">
+        <v>0</v>
+      </c>
+      <c r="G620" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Table S3 entry 7, 240 °C</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>2885.95</v>
+      </c>
+      <c r="D621" t="n">
+        <v>119348</v>
+      </c>
+      <c r="E621" t="n">
+        <v>119348</v>
+      </c>
+      <c r="F621" t="b">
+        <v>0</v>
+      </c>
+      <c r="G621" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Table S3 entry 7, 260 °C</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>2360.66</v>
+      </c>
+      <c r="D622" t="n">
+        <v>49255.1</v>
+      </c>
+      <c r="E622" t="n">
+        <v>49255.1</v>
+      </c>
+      <c r="F622" t="b">
+        <v>0</v>
+      </c>
+      <c r="G622" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Table S3 entry 7, 280 °C</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>1931.51</v>
+      </c>
+      <c r="D623" t="n">
+        <v>27695.7</v>
+      </c>
+      <c r="E623" t="n">
+        <v>27695.7</v>
+      </c>
+      <c r="F623" t="b">
+        <v>0</v>
+      </c>
+      <c r="G623" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Table S3 entry 7, 300 °C</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>1590.77</v>
+      </c>
+      <c r="D624" t="n">
+        <v>13662.5</v>
+      </c>
+      <c r="E624" t="n">
+        <v>13662.5</v>
+      </c>
+      <c r="F624" t="b">
+        <v>0</v>
+      </c>
+      <c r="G624" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Table S3 entry 7, 320 °C</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>1428.35</v>
+      </c>
+      <c r="D625" t="n">
+        <v>10419.5</v>
+      </c>
+      <c r="E625" t="n">
+        <v>10419.5</v>
+      </c>
+      <c r="F625" t="b">
+        <v>0</v>
+      </c>
+      <c r="G625" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Table S5 entry 3, 220 °C</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>6501.94</v>
+      </c>
+      <c r="D626" t="n">
+        <v>6501.94</v>
+      </c>
+      <c r="E626" t="n">
+        <v>6501.94</v>
+      </c>
+      <c r="F626" t="b">
+        <v>0</v>
+      </c>
+      <c r="G626" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Table S5 entry 3, 240 °C</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>3740.94</v>
+      </c>
+      <c r="D627" t="n">
+        <v>3740.94</v>
+      </c>
+      <c r="E627" t="n">
+        <v>3740.94</v>
+      </c>
+      <c r="F627" t="b">
+        <v>0</v>
+      </c>
+      <c r="G627" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Table S5 entry 3, 260 °C</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>2333.13</v>
+      </c>
+      <c r="D628" t="n">
+        <v>2333.13</v>
+      </c>
+      <c r="E628" t="n">
+        <v>2333.13</v>
+      </c>
+      <c r="F628" t="b">
+        <v>0</v>
+      </c>
+      <c r="G628" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Table S5 entry 3, 280 °C</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>1263.21</v>
+      </c>
+      <c r="D629" t="n">
+        <v>1263.21</v>
+      </c>
+      <c r="E629" t="n">
+        <v>1263.21</v>
+      </c>
+      <c r="F629" t="b">
+        <v>0</v>
+      </c>
+      <c r="G629" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Table S5 entry 3, 300 °C</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>1113.13</v>
+      </c>
+      <c r="D630" t="n">
+        <v>1540.04</v>
+      </c>
+      <c r="E630" t="n">
+        <v>1540.04</v>
+      </c>
+      <c r="F630" t="b">
+        <v>0</v>
+      </c>
+      <c r="G630" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Table S5 entry 4, 220 °C</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>3738.02</v>
+      </c>
+      <c r="D631" t="n">
+        <v>3738.02</v>
+      </c>
+      <c r="E631" t="n">
+        <v>3738.02</v>
+      </c>
+      <c r="F631" t="b">
+        <v>0</v>
+      </c>
+      <c r="G631" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Table S5 entry 4, 240 °C</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>2330.07</v>
+      </c>
+      <c r="D632" t="n">
+        <v>2330.07</v>
+      </c>
+      <c r="E632" t="n">
+        <v>2330.07</v>
+      </c>
+      <c r="F632" t="b">
+        <v>0</v>
+      </c>
+      <c r="G632" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Table S5 entry 4, 260 °C</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>1863.65</v>
+      </c>
+      <c r="D633" t="n">
+        <v>1863.65</v>
+      </c>
+      <c r="E633" t="n">
+        <v>1863.65</v>
+      </c>
+      <c r="F633" t="b">
+        <v>0</v>
+      </c>
+      <c r="G633" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Table S5 entry 4, 280 °C</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>1291.92</v>
+      </c>
+      <c r="D634" t="n">
+        <v>1291.92</v>
+      </c>
+      <c r="E634" t="n">
+        <v>1291.92</v>
+      </c>
+      <c r="F634" t="b">
+        <v>0</v>
+      </c>
+      <c r="G634" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Table S5 entry 4, 300 °C</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>1111.56</v>
+      </c>
+      <c r="D635" t="n">
+        <v>1636.43</v>
+      </c>
+      <c r="E635" t="n">
+        <v>1636.43</v>
+      </c>
+      <c r="F635" t="b">
+        <v>0</v>
+      </c>
+      <c r="G635" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -45944,7 +54638,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_pruning_2026_10_06/summary.json, analysis/nh3_alloy_extension_2026_10_05/nh3_1_2/summary.json (pruning) and analysis/nh3_alloy_extension_2026_10_05/nh3_1_2/alloy_chain_results.csv</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/pruning/summary.json, analysis/nh3_alloy_extension_2026_10_05/nh3_1_2/summary.json (pruning) and analysis/nh3_alloy_extension_2026_10_05/nh3_1_2/alloy_chain_results.csv</t>
         </is>
       </c>
     </row>
@@ -45982,13 +54676,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>310</v>
+        <v>632</v>
       </c>
       <c r="C4" t="n">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="D4" t="n">
-        <v>199</v>
+        <v>394</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -46001,13 +54695,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>310</v>
+        <v>632</v>
       </c>
       <c r="C5" t="n">
-        <v>212</v>
+        <v>442</v>
       </c>
       <c r="D5" t="n">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
